--- a/project/MDK_V5/AT32F403ARGT7_EG800AK_analysis.xlsx
+++ b/project/MDK_V5/AT32F403ARGT7_EG800AK_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="68">
   <si>
     <t>AT32F403ARGT7_EG800AK</t>
   </si>
@@ -23,6 +23,12 @@
     <t>heap_4.o</t>
   </si>
   <si>
+    <t>drv_eg.o</t>
+  </si>
+  <si>
+    <t>eg_service.o</t>
+  </si>
+  <si>
     <t>freertos_app.o</t>
   </si>
   <si>
@@ -35,6 +41,9 @@
     <t>timers.o</t>
   </si>
   <si>
+    <t>eg800_basic.o</t>
+  </si>
+  <si>
     <t>log.o</t>
   </si>
   <si>
@@ -62,6 +71,9 @@
     <t>printfa.o</t>
   </si>
   <si>
+    <t>lwrb.o</t>
+  </si>
+  <si>
     <t>at32f403a_407_crm.o</t>
   </si>
   <si>
@@ -74,57 +86,57 @@
     <t>at32f403a_407_dma.o</t>
   </si>
   <si>
+    <t>at32f403a_407_wk_config.o</t>
+  </si>
+  <si>
     <t>at32f403a_407_gpio.o</t>
   </si>
   <si>
-    <t>at32f403a_407_wk_config.o</t>
+    <t>at32f403a_407_misc.o</t>
+  </si>
+  <si>
+    <t>dadd.o</t>
+  </si>
+  <si>
+    <t>wk_usart.o</t>
+  </si>
+  <si>
+    <t>at32f403a_407_int.o</t>
+  </si>
+  <si>
+    <t>list.o</t>
+  </si>
+  <si>
+    <t>wk_dma.o</t>
+  </si>
+  <si>
+    <t>dmul.o</t>
+  </si>
+  <si>
+    <t>ddiv.o</t>
+  </si>
+  <si>
+    <t>depilogue.o</t>
   </si>
   <si>
     <t>at32f403a_407_exint.o</t>
   </si>
   <si>
-    <t>at32f403a_407_misc.o</t>
-  </si>
-  <si>
-    <t>dadd.o</t>
-  </si>
-  <si>
-    <t>wk_usart.o</t>
-  </si>
-  <si>
-    <t>list.o</t>
-  </si>
-  <si>
-    <t>at32f403a_407_int.o</t>
-  </si>
-  <si>
-    <t>wk_dma.o</t>
-  </si>
-  <si>
-    <t>dmul.o</t>
-  </si>
-  <si>
-    <t>ddiv.o</t>
-  </si>
-  <si>
-    <t>depilogue.o</t>
-  </si>
-  <si>
     <t>wk_gpio.o</t>
   </si>
   <si>
+    <t>uldiv.o</t>
+  </si>
+  <si>
+    <t>at32f403a_407_tmr.o</t>
+  </si>
+  <si>
+    <t>app_eg.o</t>
+  </si>
+  <si>
     <t>main.o</t>
   </si>
   <si>
-    <t>uldiv.o</t>
-  </si>
-  <si>
-    <t>at32f403a_407_tmr.o</t>
-  </si>
-  <si>
-    <t>wk_exint.o</t>
-  </si>
-  <si>
     <t>dfixul.o</t>
   </si>
   <si>
@@ -149,13 +161,25 @@
     <t>llushr.o</t>
   </si>
   <si>
+    <t>strncmp.o</t>
+  </si>
+  <si>
     <t>llshl.o</t>
   </si>
   <si>
     <t>handlers.o</t>
   </si>
   <si>
+    <t>strcmp.o</t>
+  </si>
+  <si>
+    <t>strchr.o</t>
+  </si>
+  <si>
     <t>wk_debug.o</t>
+  </si>
+  <si>
+    <t>strlen.o</t>
   </si>
   <si>
     <t>entry9a.o</t>
@@ -284,49 +308,58 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$52</c:f>
+              <c:f>ram_percent!$A$3:$A$60</c:f>
               <c:strCache>
-                <c:ptCount val="50"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>drv_eg.o</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>eg_service.o</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>freertos_app.o</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>startup_at32f403a_407.o</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>tasks.o</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="6">
                   <c:v>timers.o</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
+                  <c:v>eg800_basic.o</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>log.o</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="9">
                   <c:v>queue.o</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="10">
                   <c:v>include_port.o</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="11">
                   <c:v>mc_w.l</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="12">
                   <c:v>stdout.o</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="13">
                   <c:v>wk_system.o</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="14">
                   <c:v>system_main.o</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="15">
                   <c:v>system_at32f403a_407.o</c:v>
                 </c:pt>
-                <c:pt idx="49">
+                <c:pt idx="57">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -334,50 +367,59 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$52</c:f>
+              <c:f>ram_percent!$B$3:$B$60</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="50"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
-                  <c:v>73.47113800048828</c:v>
+                  <c:v>38.91203689575195</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>12.33102035522461</c:v>
+                  <c:v>31.36980056762695</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.324225902557373</c:v>
+                  <c:v>14.91779708862305</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.433230876922607</c:v>
+                  <c:v>6.530797958374023</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.145769357681274</c:v>
+                  <c:v>3.879081726074219</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.6294256448745728</c:v>
+                  <c:v>1.81831955909729</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.4577641189098358</c:v>
+                  <c:v>1.136449694633484</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.06437307596206665</c:v>
+                  <c:v>0.750056803226471</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.02861025743186474</c:v>
+                  <c:v>0.3333585858345032</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.02861025743186474</c:v>
+                  <c:v>0.2424426078796387</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.02861025743186474</c:v>
+                  <c:v>0.03409349173307419</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.02861025743186474</c:v>
+                  <c:v>0.01515266299247742</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.02861025743186474</c:v>
-                </c:pt>
-                <c:pt idx="49">
+                  <c:v>0.01515266299247742</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.01515266299247742</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.01515266299247742</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.01515266299247742</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -445,157 +487,181 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$52</c:f>
+              <c:f>flash_percent!$A$3:$A$60</c:f>
               <c:strCache>
-                <c:ptCount val="50"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>tasks.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>eg_service.o</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>queue.o</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>mc_w.l</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>printfa.o</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>timers.o</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
+                  <c:v>drv_eg.o</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>lwrb.o</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>at32f403a_407_crm.o</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="9">
                   <c:v>at32f403a_407_usart.o</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="10">
                   <c:v>include_port.o</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="11">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="12">
                   <c:v>mf_w.l</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="13">
                   <c:v>at32f403a_407_dma.o</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="14">
+                  <c:v>at32f403a_407_wk_config.o</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>system_at32f403a_407.o</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>at32f403a_407_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="12">
-                  <c:v>at32f403a_407_wk_config.o</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>system_at32f403a_407.o</c:v>
-                </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="17">
                   <c:v>startup_at32f403a_407.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="18">
+                  <c:v>at32f403a_407_misc.o</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>eg800_basic.o</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>log.o</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>dadd.o</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>wk_system.o</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>freertos_app.o</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>wk_usart.o</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>at32f403a_407_int.o</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>list.o</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>wk_dma.o</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>dmul.o</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>ddiv.o</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>system_main.o</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>depilogue.o</c:v>
+                </c:pt>
+                <c:pt idx="32">
                   <c:v>at32f403a_407_exint.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
-                  <c:v>at32f403a_407_misc.o</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>log.o</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>dadd.o</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>wk_system.o</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>freertos_app.o</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>wk_usart.o</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>list.o</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>at32f403a_407_int.o</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>wk_dma.o</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>dmul.o</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>ddiv.o</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>system_main.o</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>depilogue.o</c:v>
-                </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="33">
                   <c:v>wk_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="34">
+                  <c:v>uldiv.o</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>at32f403a_407_tmr.o</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>app_eg.o</c:v>
+                </c:pt>
+                <c:pt idx="37">
                   <c:v>main.o</c:v>
                 </c:pt>
-                <c:pt idx="31">
-                  <c:v>uldiv.o</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>at32f403a_407_tmr.o</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>wk_exint.o</c:v>
-                </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="38">
                   <c:v>dfixul.o</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="39">
                   <c:v>cdrcmple.o</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="40">
                   <c:v>init.o</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="41">
                   <c:v>uidiv.o</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="42">
                   <c:v>memseta.o</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="43">
                   <c:v>memcpya.o</c:v>
                 </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="44">
                   <c:v>llsshr.o</c:v>
                 </c:pt>
-                <c:pt idx="41">
+                <c:pt idx="45">
                   <c:v>llushr.o</c:v>
                 </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="46">
+                  <c:v>strncmp.o</c:v>
+                </c:pt>
+                <c:pt idx="47">
                   <c:v>llshl.o</c:v>
                 </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="48">
                   <c:v>handlers.o</c:v>
                 </c:pt>
-                <c:pt idx="44">
+                <c:pt idx="49">
+                  <c:v>strcmp.o</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>strchr.o</c:v>
+                </c:pt>
+                <c:pt idx="51">
                   <c:v>wk_debug.o</c:v>
                 </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="52">
+                  <c:v>strlen.o</c:v>
+                </c:pt>
+                <c:pt idx="53">
                   <c:v>entry9a.o</c:v>
                 </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="54">
                   <c:v>entry2.o</c:v>
                 </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="55">
                   <c:v>stdout.o</c:v>
                 </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="56">
                   <c:v>entry5.o</c:v>
                 </c:pt>
-                <c:pt idx="49">
+                <c:pt idx="57">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -603,158 +669,182 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$52</c:f>
+              <c:f>flash_percent!$B$3:$B$60</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="50"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
-                  <c:v>15.78145027160645</c:v>
+                  <c:v>14.49541282653809</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11.51647472381592</c:v>
+                  <c:v>13.89326763153076</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.312961578369141</c:v>
+                  <c:v>9.530946731567383</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.878598690032959</c:v>
+                  <c:v>7.184390544891357</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.907217025756836</c:v>
+                  <c:v>5.876728057861328</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.89207649230957</c:v>
+                  <c:v>4.406253814697266</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.046703338623047</c:v>
+                  <c:v>4.031528472900391</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.921976327896118</c:v>
+                  <c:v>3.654218912124634</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.887329816818237</c:v>
+                  <c:v>3.649050235748291</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.693309783935547</c:v>
+                  <c:v>3.018477916717529</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.118179082870483</c:v>
+                  <c:v>2.925442457199097</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.591553211212158</c:v>
+                  <c:v>2.899599313735962</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.293593883514404</c:v>
+                  <c:v>2.754877805709839</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.085715293884277</c:v>
+                  <c:v>2.362062215805054</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.469008803367615</c:v>
+                  <c:v>1.71081531047821</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.351210951805115</c:v>
+                  <c:v>1.555756568908691</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.281918048858643</c:v>
+                  <c:v>1.478227138519287</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.223019123077393</c:v>
+                  <c:v>1.095748782157898</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.157190918922424</c:v>
+                  <c:v>0.9561958909034729</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.150261521339417</c:v>
+                  <c:v>0.9458586573600769</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.132938385009766</c:v>
+                  <c:v>0.8967567086219788</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.129473686218262</c:v>
+                  <c:v>0.8631606101989746</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.025534391403198</c:v>
+                  <c:v>0.8579919934272766</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.9285244345664978</c:v>
+                  <c:v>0.8450704216957092</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.9077365398406982</c:v>
+                  <c:v>0.8424860835075378</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.7899386882781982</c:v>
+                  <c:v>0.7959684729576111</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.7691507935523987</c:v>
+                  <c:v>0.7649567127227783</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.7310397624969482</c:v>
+                  <c:v>0.677090048789978</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.6444236636161804</c:v>
+                  <c:v>0.5892233848571777</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.4573329091072083</c:v>
+                  <c:v>0.5737175345420837</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.4573329091072083</c:v>
+                  <c:v>0.5659645795822144</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.3395350575447083</c:v>
+                  <c:v>0.4806822538375855</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.3256764709949493</c:v>
+                  <c:v>0.3462979793548584</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.3118178844451904</c:v>
+                  <c:v>0.341129332780838</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.1663028746843338</c:v>
+                  <c:v>0.2532626986503601</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.1663028746843338</c:v>
+                  <c:v>0.2429254353046417</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.1663028746843338</c:v>
+                  <c:v>0.1550587862730026</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.1524443030357361</c:v>
+                  <c:v>0.1343842893838882</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.1247271597385407</c:v>
+                  <c:v>0.1240470334887505</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.1247271597385407</c:v>
+                  <c:v>0.1240470334887505</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.1247271597385407</c:v>
+                  <c:v>0.1240470334887505</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.1108685880899429</c:v>
+                  <c:v>0.1137097850441933</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.1039393022656441</c:v>
+                  <c:v>0.09303527325391769</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.1039393022656441</c:v>
+                  <c:v>0.09303527325391769</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.06236357986927033</c:v>
+                  <c:v>0.09303527325391769</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.02771714702248573</c:v>
+                  <c:v>0.0826980248093605</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.02771714702248573</c:v>
+                  <c:v>0.07752939313650131</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.01385857351124287</c:v>
+                  <c:v>0.07752939313650131</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.01385857351124287</c:v>
+                  <c:v>0.07752939313650131</c:v>
                 </c:pt>
                 <c:pt idx="49">
+                  <c:v>0.07236076891422272</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.05168626457452774</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.04651763662695885</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.03618038445711136</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.02067450620234013</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.02067450620234013</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.01033725310117006</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.01033725310117006</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -859,8 +949,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H52" totalsRowCount="1">
-  <autoFilter ref="A2:H51"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H60" totalsRowCount="1">
+  <autoFilter ref="A2:H59"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -876,8 +966,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H52" totalsRowCount="1">
-  <autoFilter ref="A2:H51"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H60" totalsRowCount="1">
+  <autoFilter ref="A2:H59"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -1177,7 +1267,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1190,28 +1280,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E2" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="G2" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="H2" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1219,7 +1309,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>73.47113800048828</v>
+        <v>38.91203689575195</v>
       </c>
       <c r="C3" s="1">
         <v>10272</v>
@@ -1245,25 +1335,25 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>12.33102035522461</v>
+        <v>31.36980056762695</v>
       </c>
       <c r="C4" s="1">
-        <v>1724</v>
+        <v>8281</v>
       </c>
       <c r="D4" s="1">
-        <v>327</v>
+        <v>1560</v>
       </c>
       <c r="E4" s="1">
-        <v>266</v>
+        <v>1398</v>
       </c>
       <c r="F4" s="1">
-        <v>61</v>
+        <v>162</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>1724</v>
+        <v>8281</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1271,25 +1361,25 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>7.324225902557373</v>
+        <v>14.91779708862305</v>
       </c>
       <c r="C5" s="1">
-        <v>1024</v>
+        <v>3938</v>
       </c>
       <c r="D5" s="1">
-        <v>424</v>
+        <v>5376</v>
       </c>
       <c r="E5" s="1">
-        <v>36</v>
+        <v>4720</v>
       </c>
       <c r="F5" s="1">
-        <v>388</v>
+        <v>656</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>1024</v>
+        <v>3938</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1297,25 +1387,25 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>3.433230876922607</v>
+        <v>6.530797958374023</v>
       </c>
       <c r="C6" s="1">
-        <v>480</v>
+        <v>1724</v>
       </c>
       <c r="D6" s="1">
-        <v>4555</v>
+        <v>327</v>
       </c>
       <c r="E6" s="1">
-        <v>4546</v>
+        <v>266</v>
       </c>
       <c r="F6" s="1">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>480</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1323,25 +1413,25 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>2.145769357681274</v>
+        <v>3.879081726074219</v>
       </c>
       <c r="C7" s="1">
-        <v>300</v>
+        <v>1024</v>
       </c>
       <c r="D7" s="1">
-        <v>1705</v>
+        <v>424</v>
       </c>
       <c r="E7" s="1">
-        <v>1692</v>
+        <v>36</v>
       </c>
       <c r="F7" s="1">
-        <v>13</v>
+        <v>388</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>300</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1349,25 +1439,25 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.6294256448745728</v>
+        <v>1.81831955909729</v>
       </c>
       <c r="C8" s="1">
-        <v>88</v>
+        <v>480</v>
       </c>
       <c r="D8" s="1">
-        <v>353</v>
+        <v>5609</v>
       </c>
       <c r="E8" s="1">
-        <v>336</v>
+        <v>5600</v>
       </c>
       <c r="F8" s="1">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>88</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1375,25 +1465,25 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.4577641189098358</v>
+        <v>1.136449694633484</v>
       </c>
       <c r="C9" s="1">
-        <v>64</v>
+        <v>300</v>
       </c>
       <c r="D9" s="1">
-        <v>3324</v>
+        <v>1705</v>
       </c>
       <c r="E9" s="1">
-        <v>3324</v>
+        <v>1692</v>
       </c>
       <c r="F9" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>64</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1401,25 +1491,25 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.06437307596206665</v>
+        <v>0.750056803226471</v>
       </c>
       <c r="C10" s="1">
-        <v>9</v>
+        <v>198</v>
       </c>
       <c r="D10" s="1">
-        <v>1132</v>
+        <v>366</v>
       </c>
       <c r="E10" s="1">
-        <v>1128</v>
+        <v>242</v>
       </c>
       <c r="F10" s="1">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="G10" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>5</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1427,25 +1517,25 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.02861025743186474</v>
+        <v>0.3333585858345032</v>
       </c>
       <c r="C11" s="1">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="D11" s="1">
-        <v>2688</v>
+        <v>347</v>
       </c>
       <c r="E11" s="1">
-        <v>2684</v>
+        <v>336</v>
       </c>
       <c r="F11" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G11" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>0</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1453,25 +1543,25 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.02861025743186474</v>
+        <v>0.2424426078796387</v>
       </c>
       <c r="C12" s="1">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="D12" s="1">
-        <v>4</v>
+        <v>3688</v>
       </c>
       <c r="E12" s="1">
-        <v>0</v>
+        <v>3688</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1479,25 +1569,25 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.02861025743186474</v>
+        <v>0.03409349173307419</v>
       </c>
       <c r="C13" s="1">
+        <v>9</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1132</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1128</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
         <v>4</v>
       </c>
-      <c r="D13" s="1">
-        <v>332</v>
-      </c>
-      <c r="E13" s="1">
-        <v>332</v>
-      </c>
-      <c r="F13" s="1">
-        <v>0</v>
-      </c>
-      <c r="G13" s="1">
-        <v>0</v>
-      </c>
       <c r="H13" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1505,25 +1595,25 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.02861025743186474</v>
+        <v>0.01515266299247742</v>
       </c>
       <c r="C14" s="1">
         <v>4</v>
       </c>
       <c r="D14" s="1">
-        <v>211</v>
+        <v>2780</v>
       </c>
       <c r="E14" s="1">
-        <v>154</v>
+        <v>2776</v>
       </c>
       <c r="F14" s="1">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H14" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1531,19 +1621,19 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.02861025743186474</v>
+        <v>0.01515266299247742</v>
       </c>
       <c r="C15" s="1">
         <v>4</v>
       </c>
       <c r="D15" s="1">
-        <v>602</v>
+        <v>4</v>
       </c>
       <c r="E15" s="1">
-        <v>582</v>
+        <v>0</v>
       </c>
       <c r="F15" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
         <v>4</v>
@@ -1552,35 +1642,113 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
-      <c r="A52" t="s">
-        <v>51</v>
-      </c>
-      <c r="B52">
+    <row r="16" spans="1:8">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0.01515266299247742</v>
+      </c>
+      <c r="C16" s="1">
+        <v>4</v>
+      </c>
+      <c r="D16" s="1">
+        <v>332</v>
+      </c>
+      <c r="E16" s="1">
+        <v>332</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0.01515266299247742</v>
+      </c>
+      <c r="C17" s="1">
+        <v>4</v>
+      </c>
+      <c r="D17" s="1">
+        <v>219</v>
+      </c>
+      <c r="E17" s="1">
+        <v>162</v>
+      </c>
+      <c r="F17" s="1">
+        <v>57</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0.01515266299247742</v>
+      </c>
+      <c r="C18" s="1">
+        <v>4</v>
+      </c>
+      <c r="D18" s="1">
+        <v>602</v>
+      </c>
+      <c r="E18" s="1">
+        <v>582</v>
+      </c>
+      <c r="F18" s="1">
+        <v>16</v>
+      </c>
+      <c r="G18" s="1">
+        <v>4</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" t="s">
+        <v>59</v>
+      </c>
+      <c r="B60">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C52">
+      <c r="C60">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D52">
+      <c r="D60">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E52">
+      <c r="E60">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F52">
+      <c r="F60">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G52">
+      <c r="G60">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H52">
+      <c r="H60">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -1596,7 +1764,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1609,45 +1777,45 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E2" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="G2" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="H2" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B3" s="2">
-        <v>15.78145027160645</v>
+        <v>14.49541282653809</v>
       </c>
       <c r="C3" s="1">
-        <v>4555</v>
+        <v>5609</v>
       </c>
       <c r="D3" s="1">
         <v>480</v>
       </c>
       <c r="E3" s="1">
-        <v>4546</v>
+        <v>5600</v>
       </c>
       <c r="F3" s="1">
         <v>9</v>
@@ -1661,77 +1829,77 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>11.51647472381592</v>
+        <v>13.89326763153076</v>
       </c>
       <c r="C4" s="1">
-        <v>3324</v>
+        <v>5376</v>
       </c>
       <c r="D4" s="1">
-        <v>64</v>
+        <v>3938</v>
       </c>
       <c r="E4" s="1">
-        <v>3324</v>
+        <v>4720</v>
       </c>
       <c r="F4" s="1">
-        <v>0</v>
+        <v>656</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>64</v>
+        <v>3938</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="2">
-        <v>9.312961578369141</v>
+        <v>9.530946731567383</v>
       </c>
       <c r="C5" s="1">
-        <v>2688</v>
+        <v>3688</v>
       </c>
       <c r="D5" s="1">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="E5" s="1">
-        <v>2684</v>
+        <v>3688</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B6" s="2">
-        <v>7.878598690032959</v>
+        <v>7.184390544891357</v>
       </c>
       <c r="C6" s="1">
-        <v>2274</v>
+        <v>2780</v>
       </c>
       <c r="D6" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E6" s="1">
-        <v>2274</v>
+        <v>2776</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
@@ -1739,149 +1907,149 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B7" s="2">
-        <v>5.907217025756836</v>
+        <v>5.876728057861328</v>
       </c>
       <c r="C7" s="1">
-        <v>1705</v>
+        <v>2274</v>
       </c>
       <c r="D7" s="1">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E7" s="1">
-        <v>1692</v>
+        <v>2274</v>
       </c>
       <c r="F7" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>4.89207649230957</v>
+        <v>4.406253814697266</v>
       </c>
       <c r="C8" s="1">
-        <v>1412</v>
+        <v>1705</v>
       </c>
       <c r="D8" s="1">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E8" s="1">
-        <v>1372</v>
+        <v>1692</v>
       </c>
       <c r="F8" s="1">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B9" s="2">
-        <v>4.046703338623047</v>
+        <v>4.031528472900391</v>
       </c>
       <c r="C9" s="1">
-        <v>1168</v>
+        <v>1560</v>
       </c>
       <c r="D9" s="1">
-        <v>0</v>
+        <v>8281</v>
       </c>
       <c r="E9" s="1">
-        <v>1168</v>
+        <v>1398</v>
       </c>
       <c r="F9" s="1">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>0</v>
+        <v>8281</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B10" s="2">
-        <v>3.921976327896118</v>
+        <v>3.654218912124634</v>
       </c>
       <c r="C10" s="1">
-        <v>1132</v>
+        <v>1414</v>
       </c>
       <c r="D10" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E10" s="1">
-        <v>1128</v>
+        <v>1414</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="B11" s="2">
-        <v>3.887329816818237</v>
+        <v>3.649050235748291</v>
       </c>
       <c r="C11" s="1">
-        <v>1122</v>
+        <v>1412</v>
       </c>
       <c r="D11" s="1">
-        <v>10272</v>
+        <v>0</v>
       </c>
       <c r="E11" s="1">
-        <v>1122</v>
+        <v>1372</v>
       </c>
       <c r="F11" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>10272</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B12" s="2">
-        <v>3.693309783935547</v>
+        <v>3.018477916717529</v>
       </c>
       <c r="C12" s="1">
-        <v>1066</v>
+        <v>1168</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
       </c>
       <c r="E12" s="1">
-        <v>1066</v>
+        <v>1168</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -1895,45 +2063,45 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>3.118179082870483</v>
+        <v>2.925442457199097</v>
       </c>
       <c r="C13" s="1">
-        <v>900</v>
+        <v>1132</v>
       </c>
       <c r="D13" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E13" s="1">
-        <v>900</v>
+        <v>1128</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H13" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="B14" s="2">
-        <v>2.591553211212158</v>
+        <v>2.899599313735962</v>
       </c>
       <c r="C14" s="1">
-        <v>748</v>
+        <v>1122</v>
       </c>
       <c r="D14" s="1">
-        <v>0</v>
+        <v>10272</v>
       </c>
       <c r="E14" s="1">
-        <v>748</v>
+        <v>1122</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -1942,24 +2110,24 @@
         <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>10272</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B15" s="2">
-        <v>2.293593883514404</v>
+        <v>2.754877805709839</v>
       </c>
       <c r="C15" s="1">
-        <v>662</v>
+        <v>1066</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
       </c>
       <c r="E15" s="1">
-        <v>662</v>
+        <v>1066</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
@@ -1973,25 +2141,25 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B16" s="2">
-        <v>2.085715293884277</v>
+        <v>2.362062215805054</v>
       </c>
       <c r="C16" s="1">
-        <v>602</v>
+        <v>914</v>
       </c>
       <c r="D16" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E16" s="1">
-        <v>582</v>
+        <v>914</v>
       </c>
       <c r="F16" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H16" s="1">
         <v>0</v>
@@ -1999,51 +2167,51 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="B17" s="2">
-        <v>1.469008803367615</v>
+        <v>1.71081531047821</v>
       </c>
       <c r="C17" s="1">
-        <v>424</v>
+        <v>662</v>
       </c>
       <c r="D17" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
       <c r="E17" s="1">
-        <v>36</v>
+        <v>662</v>
       </c>
       <c r="F17" s="1">
-        <v>388</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>1.351210951805115</v>
+        <v>1.555756568908691</v>
       </c>
       <c r="C18" s="1">
-        <v>390</v>
+        <v>602</v>
       </c>
       <c r="D18" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E18" s="1">
-        <v>390</v>
+        <v>582</v>
       </c>
       <c r="F18" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H18" s="1">
         <v>0</v>
@@ -2051,19 +2219,19 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B19" s="2">
-        <v>1.281918048858643</v>
+        <v>1.478227138519287</v>
       </c>
       <c r="C19" s="1">
-        <v>370</v>
+        <v>572</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
       <c r="E19" s="1">
-        <v>370</v>
+        <v>572</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -2077,45 +2245,45 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B20" s="2">
-        <v>1.223019123077393</v>
+        <v>1.095748782157898</v>
       </c>
       <c r="C20" s="1">
-        <v>353</v>
+        <v>424</v>
       </c>
       <c r="D20" s="1">
-        <v>88</v>
+        <v>1024</v>
       </c>
       <c r="E20" s="1">
-        <v>336</v>
+        <v>36</v>
       </c>
       <c r="F20" s="1">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
       </c>
       <c r="H20" s="1">
-        <v>88</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B21" s="2">
-        <v>1.157190918922424</v>
+        <v>0.9561958909034729</v>
       </c>
       <c r="C21" s="1">
-        <v>334</v>
+        <v>370</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>334</v>
+        <v>370</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -2129,71 +2297,71 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B22" s="2">
-        <v>1.150261521339417</v>
+        <v>0.9458586573600769</v>
       </c>
       <c r="C22" s="1">
-        <v>332</v>
+        <v>366</v>
       </c>
       <c r="D22" s="1">
-        <v>4</v>
+        <v>198</v>
       </c>
       <c r="E22" s="1">
-        <v>332</v>
+        <v>242</v>
       </c>
       <c r="F22" s="1">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="G22" s="1">
         <v>0</v>
       </c>
       <c r="H22" s="1">
-        <v>4</v>
+        <v>198</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B23" s="2">
-        <v>1.132938385009766</v>
+        <v>0.8967567086219788</v>
       </c>
       <c r="C23" s="1">
-        <v>327</v>
+        <v>347</v>
       </c>
       <c r="D23" s="1">
-        <v>1724</v>
+        <v>88</v>
       </c>
       <c r="E23" s="1">
-        <v>266</v>
+        <v>336</v>
       </c>
       <c r="F23" s="1">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="G23" s="1">
         <v>0</v>
       </c>
       <c r="H23" s="1">
-        <v>1724</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B24" s="2">
-        <v>1.129473686218262</v>
+        <v>0.8631606101989746</v>
       </c>
       <c r="C24" s="1">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
       </c>
       <c r="E24" s="1">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -2207,19 +2375,19 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B25" s="2">
-        <v>1.025534391403198</v>
+        <v>0.8579919934272766</v>
       </c>
       <c r="C25" s="1">
-        <v>296</v>
+        <v>332</v>
       </c>
       <c r="D25" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E25" s="1">
-        <v>296</v>
+        <v>332</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -2228,33 +2396,33 @@
         <v>0</v>
       </c>
       <c r="H25" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="B26" s="2">
-        <v>0.9285244345664978</v>
+        <v>0.8450704216957092</v>
       </c>
       <c r="C26" s="1">
-        <v>268</v>
+        <v>327</v>
       </c>
       <c r="D26" s="1">
-        <v>0</v>
+        <v>1724</v>
       </c>
       <c r="E26" s="1">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F26" s="1">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="G26" s="1">
         <v>0</v>
       </c>
       <c r="H26" s="1">
-        <v>0</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -2262,16 +2430,16 @@
         <v>27</v>
       </c>
       <c r="B27" s="2">
-        <v>0.9077365398406982</v>
+        <v>0.8424860835075378</v>
       </c>
       <c r="C27" s="1">
-        <v>262</v>
+        <v>326</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
       </c>
       <c r="E27" s="1">
-        <v>262</v>
+        <v>326</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
@@ -2288,16 +2456,16 @@
         <v>28</v>
       </c>
       <c r="B28" s="2">
-        <v>0.7899386882781982</v>
+        <v>0.7959684729576111</v>
       </c>
       <c r="C28" s="1">
-        <v>228</v>
+        <v>308</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
       </c>
       <c r="E28" s="1">
-        <v>228</v>
+        <v>308</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -2314,16 +2482,16 @@
         <v>29</v>
       </c>
       <c r="B29" s="2">
-        <v>0.7691507935523987</v>
+        <v>0.7649567127227783</v>
       </c>
       <c r="C29" s="1">
-        <v>222</v>
+        <v>296</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="1">
-        <v>222</v>
+        <v>296</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -2337,45 +2505,45 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="B30" s="2">
-        <v>0.7310397624969482</v>
+        <v>0.677090048789978</v>
       </c>
       <c r="C30" s="1">
-        <v>211</v>
+        <v>262</v>
       </c>
       <c r="D30" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E30" s="1">
-        <v>154</v>
+        <v>262</v>
       </c>
       <c r="F30" s="1">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="G30" s="1">
         <v>0</v>
       </c>
       <c r="H30" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B31" s="2">
-        <v>0.6444236636161804</v>
+        <v>0.5892233848571777</v>
       </c>
       <c r="C31" s="1">
-        <v>186</v>
+        <v>228</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
       </c>
       <c r="E31" s="1">
-        <v>186</v>
+        <v>228</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
@@ -2389,19 +2557,19 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B32" s="2">
-        <v>0.4573329091072083</v>
+        <v>0.5737175345420837</v>
       </c>
       <c r="C32" s="1">
-        <v>132</v>
+        <v>222</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
       </c>
       <c r="E32" s="1">
-        <v>132</v>
+        <v>222</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -2415,28 +2583,28 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B33" s="2">
-        <v>0.4573329091072083</v>
+        <v>0.5659645795822144</v>
       </c>
       <c r="C33" s="1">
-        <v>132</v>
+        <v>219</v>
       </c>
       <c r="D33" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E33" s="1">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="F33" s="1">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="G33" s="1">
         <v>0</v>
       </c>
       <c r="H33" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -2444,16 +2612,16 @@
         <v>33</v>
       </c>
       <c r="B34" s="2">
-        <v>0.3395350575447083</v>
+        <v>0.4806822538375855</v>
       </c>
       <c r="C34" s="1">
-        <v>98</v>
+        <v>186</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
       </c>
       <c r="E34" s="1">
-        <v>98</v>
+        <v>186</v>
       </c>
       <c r="F34" s="1">
         <v>0</v>
@@ -2470,16 +2638,16 @@
         <v>34</v>
       </c>
       <c r="B35" s="2">
-        <v>0.3256764709949493</v>
+        <v>0.3462979793548584</v>
       </c>
       <c r="C35" s="1">
-        <v>94</v>
+        <v>134</v>
       </c>
       <c r="D35" s="1">
         <v>0</v>
       </c>
       <c r="E35" s="1">
-        <v>94</v>
+        <v>134</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -2496,16 +2664,16 @@
         <v>35</v>
       </c>
       <c r="B36" s="2">
-        <v>0.3118178844451904</v>
+        <v>0.341129332780838</v>
       </c>
       <c r="C36" s="1">
-        <v>90</v>
+        <v>132</v>
       </c>
       <c r="D36" s="1">
         <v>0</v>
       </c>
       <c r="E36" s="1">
-        <v>90</v>
+        <v>132</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
@@ -2522,16 +2690,16 @@
         <v>36</v>
       </c>
       <c r="B37" s="2">
-        <v>0.1663028746843338</v>
+        <v>0.2532626986503601</v>
       </c>
       <c r="C37" s="1">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="D37" s="1">
         <v>0</v>
       </c>
       <c r="E37" s="1">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
@@ -2548,16 +2716,16 @@
         <v>37</v>
       </c>
       <c r="B38" s="2">
-        <v>0.1663028746843338</v>
+        <v>0.2429254353046417</v>
       </c>
       <c r="C38" s="1">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="D38" s="1">
         <v>0</v>
       </c>
       <c r="E38" s="1">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
@@ -2574,16 +2742,16 @@
         <v>38</v>
       </c>
       <c r="B39" s="2">
-        <v>0.1663028746843338</v>
+        <v>0.1550587862730026</v>
       </c>
       <c r="C39" s="1">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="D39" s="1">
         <v>0</v>
       </c>
       <c r="E39" s="1">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F39" s="1">
         <v>0</v>
@@ -2600,16 +2768,16 @@
         <v>39</v>
       </c>
       <c r="B40" s="2">
-        <v>0.1524443030357361</v>
+        <v>0.1343842893838882</v>
       </c>
       <c r="C40" s="1">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D40" s="1">
         <v>0</v>
       </c>
       <c r="E40" s="1">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
@@ -2626,16 +2794,16 @@
         <v>40</v>
       </c>
       <c r="B41" s="2">
-        <v>0.1247271597385407</v>
+        <v>0.1240470334887505</v>
       </c>
       <c r="C41" s="1">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D41" s="1">
         <v>0</v>
       </c>
       <c r="E41" s="1">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
@@ -2652,16 +2820,16 @@
         <v>41</v>
       </c>
       <c r="B42" s="2">
-        <v>0.1247271597385407</v>
+        <v>0.1240470334887505</v>
       </c>
       <c r="C42" s="1">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D42" s="1">
         <v>0</v>
       </c>
       <c r="E42" s="1">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F42" s="1">
         <v>0</v>
@@ -2678,16 +2846,16 @@
         <v>42</v>
       </c>
       <c r="B43" s="2">
-        <v>0.1247271597385407</v>
+        <v>0.1240470334887505</v>
       </c>
       <c r="C43" s="1">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D43" s="1">
         <v>0</v>
       </c>
       <c r="E43" s="1">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
@@ -2704,16 +2872,16 @@
         <v>43</v>
       </c>
       <c r="B44" s="2">
-        <v>0.1108685880899429</v>
+        <v>0.1137097850441933</v>
       </c>
       <c r="C44" s="1">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D44" s="1">
         <v>0</v>
       </c>
       <c r="E44" s="1">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
@@ -2730,16 +2898,16 @@
         <v>44</v>
       </c>
       <c r="B45" s="2">
-        <v>0.1039393022656441</v>
+        <v>0.09303527325391769</v>
       </c>
       <c r="C45" s="1">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D45" s="1">
         <v>0</v>
       </c>
       <c r="E45" s="1">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
@@ -2756,16 +2924,16 @@
         <v>45</v>
       </c>
       <c r="B46" s="2">
-        <v>0.1039393022656441</v>
+        <v>0.09303527325391769</v>
       </c>
       <c r="C46" s="1">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D46" s="1">
         <v>0</v>
       </c>
       <c r="E46" s="1">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
@@ -2782,16 +2950,16 @@
         <v>46</v>
       </c>
       <c r="B47" s="2">
-        <v>0.06236357986927033</v>
+        <v>0.09303527325391769</v>
       </c>
       <c r="C47" s="1">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="D47" s="1">
         <v>0</v>
       </c>
       <c r="E47" s="1">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F47" s="1">
         <v>0</v>
@@ -2808,16 +2976,16 @@
         <v>47</v>
       </c>
       <c r="B48" s="2">
-        <v>0.02771714702248573</v>
+        <v>0.0826980248093605</v>
       </c>
       <c r="C48" s="1">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D48" s="1">
         <v>0</v>
       </c>
       <c r="E48" s="1">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
@@ -2834,16 +3002,16 @@
         <v>48</v>
       </c>
       <c r="B49" s="2">
-        <v>0.02771714702248573</v>
+        <v>0.07752939313650131</v>
       </c>
       <c r="C49" s="1">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D49" s="1">
         <v>0</v>
       </c>
       <c r="E49" s="1">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
@@ -2857,25 +3025,25 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="B50" s="2">
-        <v>0.01385857351124287</v>
+        <v>0.07752939313650131</v>
       </c>
       <c r="C50" s="1">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D50" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E50" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
       </c>
       <c r="G50" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H50" s="1">
         <v>0</v>
@@ -2883,59 +3051,267 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B51" s="2">
-        <v>0.01385857351124287</v>
+        <v>0.07752939313650131</v>
       </c>
       <c r="C51" s="1">
+        <v>30</v>
+      </c>
+      <c r="D51" s="1">
+        <v>0</v>
+      </c>
+      <c r="E51" s="1">
+        <v>30</v>
+      </c>
+      <c r="F51" s="1">
+        <v>0</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0</v>
+      </c>
+      <c r="H51" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2">
+        <v>0.07236076891422272</v>
+      </c>
+      <c r="C52" s="1">
+        <v>28</v>
+      </c>
+      <c r="D52" s="1">
+        <v>0</v>
+      </c>
+      <c r="E52" s="1">
+        <v>28</v>
+      </c>
+      <c r="F52" s="1">
+        <v>0</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0</v>
+      </c>
+      <c r="H52" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2">
+        <v>0.05168626457452774</v>
+      </c>
+      <c r="C53" s="1">
+        <v>20</v>
+      </c>
+      <c r="D53" s="1">
+        <v>0</v>
+      </c>
+      <c r="E53" s="1">
+        <v>20</v>
+      </c>
+      <c r="F53" s="1">
+        <v>0</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0</v>
+      </c>
+      <c r="H53" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2">
+        <v>0.04651763662695885</v>
+      </c>
+      <c r="C54" s="1">
+        <v>18</v>
+      </c>
+      <c r="D54" s="1">
+        <v>0</v>
+      </c>
+      <c r="E54" s="1">
+        <v>18</v>
+      </c>
+      <c r="F54" s="1">
+        <v>0</v>
+      </c>
+      <c r="G54" s="1">
+        <v>0</v>
+      </c>
+      <c r="H54" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2">
+        <v>0.03618038445711136</v>
+      </c>
+      <c r="C55" s="1">
+        <v>14</v>
+      </c>
+      <c r="D55" s="1">
+        <v>0</v>
+      </c>
+      <c r="E55" s="1">
+        <v>14</v>
+      </c>
+      <c r="F55" s="1">
+        <v>0</v>
+      </c>
+      <c r="G55" s="1">
+        <v>0</v>
+      </c>
+      <c r="H55" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2">
+        <v>0.02067450620234013</v>
+      </c>
+      <c r="C56" s="1">
+        <v>8</v>
+      </c>
+      <c r="D56" s="1">
+        <v>0</v>
+      </c>
+      <c r="E56" s="1">
+        <v>8</v>
+      </c>
+      <c r="F56" s="1">
+        <v>0</v>
+      </c>
+      <c r="G56" s="1">
+        <v>0</v>
+      </c>
+      <c r="H56" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2">
+        <v>0.02067450620234013</v>
+      </c>
+      <c r="C57" s="1">
+        <v>8</v>
+      </c>
+      <c r="D57" s="1">
+        <v>0</v>
+      </c>
+      <c r="E57" s="1">
+        <v>8</v>
+      </c>
+      <c r="F57" s="1">
+        <v>0</v>
+      </c>
+      <c r="G57" s="1">
+        <v>0</v>
+      </c>
+      <c r="H57" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B58" s="2">
+        <v>0.01033725310117006</v>
+      </c>
+      <c r="C58" s="1">
         <v>4</v>
       </c>
-      <c r="D51" s="1">
-        <v>0</v>
-      </c>
-      <c r="E51" s="1">
+      <c r="D58" s="1">
         <v>4</v>
       </c>
-      <c r="F51" s="1">
-        <v>0</v>
-      </c>
-      <c r="G51" s="1">
-        <v>0</v>
-      </c>
-      <c r="H51" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" t="s">
-        <v>51</v>
-      </c>
-      <c r="B52">
+      <c r="E58" s="1">
+        <v>0</v>
+      </c>
+      <c r="F58" s="1">
+        <v>0</v>
+      </c>
+      <c r="G58" s="1">
+        <v>4</v>
+      </c>
+      <c r="H58" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B59" s="2">
+        <v>0.01033725310117006</v>
+      </c>
+      <c r="C59" s="1">
+        <v>4</v>
+      </c>
+      <c r="D59" s="1">
+        <v>0</v>
+      </c>
+      <c r="E59" s="1">
+        <v>4</v>
+      </c>
+      <c r="F59" s="1">
+        <v>0</v>
+      </c>
+      <c r="G59" s="1">
+        <v>0</v>
+      </c>
+      <c r="H59" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" t="s">
+        <v>59</v>
+      </c>
+      <c r="B60">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C52">
+      <c r="C60">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D52">
+      <c r="D60">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E52">
+      <c r="E60">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F52">
+      <c r="F60">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G52">
+      <c r="G60">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H52">
+      <c r="H60">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/project/MDK_V5/AT32F403ARGT7_EG800AK_analysis.xlsx
+++ b/project/MDK_V5/AT32F403ARGT7_EG800AK_analysis.xlsx
@@ -41,7 +41,7 @@
     <t>timers.o</t>
   </si>
   <si>
-    <t>eg800_basic.o</t>
+    <t>eg_basic.o</t>
   </si>
   <si>
     <t>log.o</t>
@@ -333,7 +333,7 @@
                   <c:v>timers.o</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>eg800_basic.o</c:v>
+                  <c:v>eg_basic.o</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>log.o</c:v>
@@ -372,52 +372,52 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="58"/>
                 <c:pt idx="0">
-                  <c:v>38.91203689575195</c:v>
+                  <c:v>38.90614318847656</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>31.36980056762695</c:v>
+                  <c:v>31.36504745483398</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>14.91779708862305</c:v>
+                  <c:v>14.93068695068359</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.530797958374023</c:v>
+                  <c:v>6.529808521270752</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.879081726074219</c:v>
+                  <c:v>3.878494024276733</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.81831955909729</c:v>
+                  <c:v>1.818044066429138</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.136449694633484</c:v>
+                  <c:v>1.136277556419373</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.750056803226471</c:v>
+                  <c:v>0.7499431967735291</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.3333585858345032</c:v>
+                  <c:v>0.333308070898056</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.2424426078796387</c:v>
+                  <c:v>0.2424058765172958</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.03409349173307419</c:v>
+                  <c:v>0.03408832848072052</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.01515266299247742</c:v>
+                  <c:v>0.01515036728233099</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.01515266299247742</c:v>
+                  <c:v>0.01515036728233099</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.01515266299247742</c:v>
+                  <c:v>0.01515036728233099</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.01515266299247742</c:v>
+                  <c:v>0.01515036728233099</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.01515266299247742</c:v>
+                  <c:v>0.01515036728233099</c:v>
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>0</c:v>
@@ -491,10 +491,10 @@
               <c:strCache>
                 <c:ptCount val="58"/>
                 <c:pt idx="0">
+                  <c:v>eg_service.o</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>tasks.o</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>eg_service.o</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>queue.o</c:v>
@@ -548,7 +548,7 @@
                   <c:v>at32f403a_407_misc.o</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>eg800_basic.o</c:v>
+                  <c:v>eg_basic.o</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>log.o</c:v>
@@ -674,175 +674,175 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="58"/>
                 <c:pt idx="0">
-                  <c:v>14.49541282653809</c:v>
+                  <c:v>16.22632789611816</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>13.89326763153076</c:v>
+                  <c:v>13.13123607635498</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.530946731567383</c:v>
+                  <c:v>9.387089729309082</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.184390544891357</c:v>
+                  <c:v>7.075952053070068</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.876728057861328</c:v>
+                  <c:v>5.788026809692383</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.406253814697266</c:v>
+                  <c:v>4.339747428894043</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.031528472900391</c:v>
+                  <c:v>4.082671642303467</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.654218912124634</c:v>
+                  <c:v>3.599063396453857</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.649050235748291</c:v>
+                  <c:v>3.593972682952881</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.018477916717529</c:v>
+                  <c:v>2.972918033599854</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.925442457199097</c:v>
+                  <c:v>2.881286859512329</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.899599313735962</c:v>
+                  <c:v>2.855833768844605</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.754877805709839</c:v>
+                  <c:v>2.71329665184021</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.362062215805054</c:v>
+                  <c:v>2.326410055160523</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.71081531047821</c:v>
+                  <c:v>1.684992909431458</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.555756568908691</c:v>
+                  <c:v>1.532274484634399</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.478227138519287</c:v>
+                  <c:v>1.455915331840515</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.095748782157898</c:v>
+                  <c:v>1.079209923744202</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.9561958909034729</c:v>
+                  <c:v>0.9417634010314941</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.9458586573600769</c:v>
+                  <c:v>0.9315821528434753</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.8967567086219788</c:v>
+                  <c:v>0.8832213282585144</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.8631606101989746</c:v>
+                  <c:v>0.8501323461532593</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.8579919934272766</c:v>
+                  <c:v>0.8450417518615723</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.8450704216957092</c:v>
+                  <c:v>0.83231520652771</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.8424860835075378</c:v>
+                  <c:v>0.8297699093818665</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.7959684729576111</c:v>
+                  <c:v>0.783954381942749</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.7649567127227783</c:v>
+                  <c:v>0.7534106969833374</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.677090048789978</c:v>
+                  <c:v>0.6668702960014343</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.5892233848571777</c:v>
+                  <c:v>0.5803298950195313</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.5737175345420837</c:v>
+                  <c:v>0.5650580525398254</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.5659645795822144</c:v>
+                  <c:v>0.5574221014976502</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.4806822538375855</c:v>
+                  <c:v>0.4734269976615906</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.3462979793548584</c:v>
+                  <c:v>0.3410710692405701</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.341129332780838</c:v>
+                  <c:v>0.3359804451465607</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.2532626986503601</c:v>
+                  <c:v>0.2494400292634964</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.2429254353046417</c:v>
+                  <c:v>0.2392588108778</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.1550587862730026</c:v>
+                  <c:v>0.1527183800935745</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.1343842893838882</c:v>
+                  <c:v>0.1323559284210205</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.1240470334887505</c:v>
+                  <c:v>0.1221747100353241</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.1240470334887505</c:v>
+                  <c:v>0.1221747100353241</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.1240470334887505</c:v>
+                  <c:v>0.1221747100353241</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.1137097850441933</c:v>
+                  <c:v>0.1119934841990471</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.09303527325391769</c:v>
+                  <c:v>0.09163103252649307</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.09303527325391769</c:v>
+                  <c:v>0.09163103252649307</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.09303527325391769</c:v>
+                  <c:v>0.09163103252649307</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.0826980248093605</c:v>
+                  <c:v>0.08144980669021606</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.07752939313650131</c:v>
+                  <c:v>0.07635919004678726</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.07752939313650131</c:v>
+                  <c:v>0.07635919004678726</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.07752939313650131</c:v>
+                  <c:v>0.07635919004678726</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.07236076891422272</c:v>
+                  <c:v>0.07126858085393906</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.05168626457452774</c:v>
+                  <c:v>0.05090612918138504</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.04651763662695885</c:v>
+                  <c:v>0.04581551626324654</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.03618038445711136</c:v>
+                  <c:v>0.03563429042696953</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.02067450620234013</c:v>
+                  <c:v>0.02036245167255402</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.02067450620234013</c:v>
+                  <c:v>0.02036245167255402</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.01033725310117006</c:v>
+                  <c:v>0.01018122583627701</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.01033725310117006</c:v>
+                  <c:v>0.01018122583627701</c:v>
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>0</c:v>
@@ -1309,7 +1309,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>38.91203689575195</v>
+        <v>38.90614318847656</v>
       </c>
       <c r="C3" s="1">
         <v>10272</v>
@@ -1335,16 +1335,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>31.36980056762695</v>
+        <v>31.36504745483398</v>
       </c>
       <c r="C4" s="1">
         <v>8281</v>
       </c>
       <c r="D4" s="1">
-        <v>1560</v>
+        <v>1604</v>
       </c>
       <c r="E4" s="1">
-        <v>1398</v>
+        <v>1442</v>
       </c>
       <c r="F4" s="1">
         <v>162</v>
@@ -1361,25 +1361,25 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>14.91779708862305</v>
+        <v>14.93068695068359</v>
       </c>
       <c r="C5" s="1">
-        <v>3938</v>
+        <v>3942</v>
       </c>
       <c r="D5" s="1">
-        <v>5376</v>
+        <v>6375</v>
       </c>
       <c r="E5" s="1">
-        <v>4720</v>
+        <v>5558</v>
       </c>
       <c r="F5" s="1">
-        <v>656</v>
+        <v>817</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>3938</v>
+        <v>3942</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1387,7 +1387,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>6.530797958374023</v>
+        <v>6.529808521270752</v>
       </c>
       <c r="C6" s="1">
         <v>1724</v>
@@ -1413,7 +1413,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>3.879081726074219</v>
+        <v>3.878494024276733</v>
       </c>
       <c r="C7" s="1">
         <v>1024</v>
@@ -1439,16 +1439,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>1.81831955909729</v>
+        <v>1.818044066429138</v>
       </c>
       <c r="C8" s="1">
         <v>480</v>
       </c>
       <c r="D8" s="1">
-        <v>5609</v>
+        <v>5159</v>
       </c>
       <c r="E8" s="1">
-        <v>5600</v>
+        <v>5150</v>
       </c>
       <c r="F8" s="1">
         <v>9</v>
@@ -1465,7 +1465,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>1.136449694633484</v>
+        <v>1.136277556419373</v>
       </c>
       <c r="C9" s="1">
         <v>300</v>
@@ -1491,7 +1491,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.750056803226471</v>
+        <v>0.7499431967735291</v>
       </c>
       <c r="C10" s="1">
         <v>198</v>
@@ -1517,7 +1517,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.3333585858345032</v>
+        <v>0.333308070898056</v>
       </c>
       <c r="C11" s="1">
         <v>88</v>
@@ -1543,7 +1543,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.2424426078796387</v>
+        <v>0.2424058765172958</v>
       </c>
       <c r="C12" s="1">
         <v>64</v>
@@ -1569,7 +1569,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.03409349173307419</v>
+        <v>0.03408832848072052</v>
       </c>
       <c r="C13" s="1">
         <v>9</v>
@@ -1595,7 +1595,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.01515266299247742</v>
+        <v>0.01515036728233099</v>
       </c>
       <c r="C14" s="1">
         <v>4</v>
@@ -1621,7 +1621,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.01515266299247742</v>
+        <v>0.01515036728233099</v>
       </c>
       <c r="C15" s="1">
         <v>4</v>
@@ -1647,7 +1647,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.01515266299247742</v>
+        <v>0.01515036728233099</v>
       </c>
       <c r="C16" s="1">
         <v>4</v>
@@ -1673,7 +1673,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.01515266299247742</v>
+        <v>0.01515036728233099</v>
       </c>
       <c r="C17" s="1">
         <v>4</v>
@@ -1699,7 +1699,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.01515266299247742</v>
+        <v>0.01515036728233099</v>
       </c>
       <c r="C18" s="1">
         <v>4</v>
@@ -1803,54 +1803,54 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" s="2">
-        <v>14.49541282653809</v>
+        <v>16.22632789611816</v>
       </c>
       <c r="C3" s="1">
-        <v>5609</v>
+        <v>6375</v>
       </c>
       <c r="D3" s="1">
-        <v>480</v>
+        <v>3942</v>
       </c>
       <c r="E3" s="1">
-        <v>5600</v>
+        <v>5558</v>
       </c>
       <c r="F3" s="1">
-        <v>9</v>
+        <v>817</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
       </c>
       <c r="H3" s="1">
-        <v>480</v>
+        <v>3942</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B4" s="2">
-        <v>13.89326763153076</v>
+        <v>13.13123607635498</v>
       </c>
       <c r="C4" s="1">
-        <v>5376</v>
+        <v>5159</v>
       </c>
       <c r="D4" s="1">
-        <v>3938</v>
+        <v>480</v>
       </c>
       <c r="E4" s="1">
-        <v>4720</v>
+        <v>5150</v>
       </c>
       <c r="F4" s="1">
-        <v>656</v>
+        <v>9</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>3938</v>
+        <v>480</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1858,7 +1858,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="2">
-        <v>9.530946731567383</v>
+        <v>9.387089729309082</v>
       </c>
       <c r="C5" s="1">
         <v>3688</v>
@@ -1884,7 +1884,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="2">
-        <v>7.184390544891357</v>
+        <v>7.075952053070068</v>
       </c>
       <c r="C6" s="1">
         <v>2780</v>
@@ -1910,7 +1910,7 @@
         <v>17</v>
       </c>
       <c r="B7" s="2">
-        <v>5.876728057861328</v>
+        <v>5.788026809692383</v>
       </c>
       <c r="C7" s="1">
         <v>2274</v>
@@ -1936,7 +1936,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>4.406253814697266</v>
+        <v>4.339747428894043</v>
       </c>
       <c r="C8" s="1">
         <v>1705</v>
@@ -1962,16 +1962,16 @@
         <v>2</v>
       </c>
       <c r="B9" s="2">
-        <v>4.031528472900391</v>
+        <v>4.082671642303467</v>
       </c>
       <c r="C9" s="1">
-        <v>1560</v>
+        <v>1604</v>
       </c>
       <c r="D9" s="1">
         <v>8281</v>
       </c>
       <c r="E9" s="1">
-        <v>1398</v>
+        <v>1442</v>
       </c>
       <c r="F9" s="1">
         <v>162</v>
@@ -1988,7 +1988,7 @@
         <v>18</v>
       </c>
       <c r="B10" s="2">
-        <v>3.654218912124634</v>
+        <v>3.599063396453857</v>
       </c>
       <c r="C10" s="1">
         <v>1414</v>
@@ -2014,7 +2014,7 @@
         <v>19</v>
       </c>
       <c r="B11" s="2">
-        <v>3.649050235748291</v>
+        <v>3.593972682952881</v>
       </c>
       <c r="C11" s="1">
         <v>1412</v>
@@ -2040,7 +2040,7 @@
         <v>20</v>
       </c>
       <c r="B12" s="2">
-        <v>3.018477916717529</v>
+        <v>2.972918033599854</v>
       </c>
       <c r="C12" s="1">
         <v>1168</v>
@@ -2066,7 +2066,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>2.925442457199097</v>
+        <v>2.881286859512329</v>
       </c>
       <c r="C13" s="1">
         <v>1132</v>
@@ -2092,7 +2092,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="2">
-        <v>2.899599313735962</v>
+        <v>2.855833768844605</v>
       </c>
       <c r="C14" s="1">
         <v>1122</v>
@@ -2118,7 +2118,7 @@
         <v>21</v>
       </c>
       <c r="B15" s="2">
-        <v>2.754877805709839</v>
+        <v>2.71329665184021</v>
       </c>
       <c r="C15" s="1">
         <v>1066</v>
@@ -2144,7 +2144,7 @@
         <v>22</v>
       </c>
       <c r="B16" s="2">
-        <v>2.362062215805054</v>
+        <v>2.326410055160523</v>
       </c>
       <c r="C16" s="1">
         <v>914</v>
@@ -2170,7 +2170,7 @@
         <v>23</v>
       </c>
       <c r="B17" s="2">
-        <v>1.71081531047821</v>
+        <v>1.684992909431458</v>
       </c>
       <c r="C17" s="1">
         <v>662</v>
@@ -2196,7 +2196,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>1.555756568908691</v>
+        <v>1.532274484634399</v>
       </c>
       <c r="C18" s="1">
         <v>602</v>
@@ -2222,7 +2222,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="2">
-        <v>1.478227138519287</v>
+        <v>1.455915331840515</v>
       </c>
       <c r="C19" s="1">
         <v>572</v>
@@ -2248,7 +2248,7 @@
         <v>5</v>
       </c>
       <c r="B20" s="2">
-        <v>1.095748782157898</v>
+        <v>1.079209923744202</v>
       </c>
       <c r="C20" s="1">
         <v>424</v>
@@ -2274,7 +2274,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="2">
-        <v>0.9561958909034729</v>
+        <v>0.9417634010314941</v>
       </c>
       <c r="C21" s="1">
         <v>370</v>
@@ -2300,7 +2300,7 @@
         <v>8</v>
       </c>
       <c r="B22" s="2">
-        <v>0.9458586573600769</v>
+        <v>0.9315821528434753</v>
       </c>
       <c r="C22" s="1">
         <v>366</v>
@@ -2326,7 +2326,7 @@
         <v>9</v>
       </c>
       <c r="B23" s="2">
-        <v>0.8967567086219788</v>
+        <v>0.8832213282585144</v>
       </c>
       <c r="C23" s="1">
         <v>347</v>
@@ -2352,7 +2352,7 @@
         <v>26</v>
       </c>
       <c r="B24" s="2">
-        <v>0.8631606101989746</v>
+        <v>0.8501323461532593</v>
       </c>
       <c r="C24" s="1">
         <v>334</v>
@@ -2378,7 +2378,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="2">
-        <v>0.8579919934272766</v>
+        <v>0.8450417518615723</v>
       </c>
       <c r="C25" s="1">
         <v>332</v>
@@ -2404,7 +2404,7 @@
         <v>4</v>
       </c>
       <c r="B26" s="2">
-        <v>0.8450704216957092</v>
+        <v>0.83231520652771</v>
       </c>
       <c r="C26" s="1">
         <v>327</v>
@@ -2430,7 +2430,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="2">
-        <v>0.8424860835075378</v>
+        <v>0.8297699093818665</v>
       </c>
       <c r="C27" s="1">
         <v>326</v>
@@ -2456,7 +2456,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="2">
-        <v>0.7959684729576111</v>
+        <v>0.783954381942749</v>
       </c>
       <c r="C28" s="1">
         <v>308</v>
@@ -2482,7 +2482,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="2">
-        <v>0.7649567127227783</v>
+        <v>0.7534106969833374</v>
       </c>
       <c r="C29" s="1">
         <v>296</v>
@@ -2508,7 +2508,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="2">
-        <v>0.677090048789978</v>
+        <v>0.6668702960014343</v>
       </c>
       <c r="C30" s="1">
         <v>262</v>
@@ -2534,7 +2534,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="2">
-        <v>0.5892233848571777</v>
+        <v>0.5803298950195313</v>
       </c>
       <c r="C31" s="1">
         <v>228</v>
@@ -2560,7 +2560,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="2">
-        <v>0.5737175345420837</v>
+        <v>0.5650580525398254</v>
       </c>
       <c r="C32" s="1">
         <v>222</v>
@@ -2586,7 +2586,7 @@
         <v>15</v>
       </c>
       <c r="B33" s="2">
-        <v>0.5659645795822144</v>
+        <v>0.5574221014976502</v>
       </c>
       <c r="C33" s="1">
         <v>219</v>
@@ -2612,7 +2612,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="2">
-        <v>0.4806822538375855</v>
+        <v>0.4734269976615906</v>
       </c>
       <c r="C34" s="1">
         <v>186</v>
@@ -2638,7 +2638,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="2">
-        <v>0.3462979793548584</v>
+        <v>0.3410710692405701</v>
       </c>
       <c r="C35" s="1">
         <v>134</v>
@@ -2664,7 +2664,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="2">
-        <v>0.341129332780838</v>
+        <v>0.3359804451465607</v>
       </c>
       <c r="C36" s="1">
         <v>132</v>
@@ -2690,7 +2690,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="2">
-        <v>0.2532626986503601</v>
+        <v>0.2494400292634964</v>
       </c>
       <c r="C37" s="1">
         <v>98</v>
@@ -2716,7 +2716,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="2">
-        <v>0.2429254353046417</v>
+        <v>0.2392588108778</v>
       </c>
       <c r="C38" s="1">
         <v>94</v>
@@ -2742,7 +2742,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="2">
-        <v>0.1550587862730026</v>
+        <v>0.1527183800935745</v>
       </c>
       <c r="C39" s="1">
         <v>60</v>
@@ -2768,7 +2768,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="2">
-        <v>0.1343842893838882</v>
+        <v>0.1323559284210205</v>
       </c>
       <c r="C40" s="1">
         <v>52</v>
@@ -2794,7 +2794,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="2">
-        <v>0.1240470334887505</v>
+        <v>0.1221747100353241</v>
       </c>
       <c r="C41" s="1">
         <v>48</v>
@@ -2820,7 +2820,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="2">
-        <v>0.1240470334887505</v>
+        <v>0.1221747100353241</v>
       </c>
       <c r="C42" s="1">
         <v>48</v>
@@ -2846,7 +2846,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="2">
-        <v>0.1240470334887505</v>
+        <v>0.1221747100353241</v>
       </c>
       <c r="C43" s="1">
         <v>48</v>
@@ -2872,7 +2872,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="2">
-        <v>0.1137097850441933</v>
+        <v>0.1119934841990471</v>
       </c>
       <c r="C44" s="1">
         <v>44</v>
@@ -2898,7 +2898,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="2">
-        <v>0.09303527325391769</v>
+        <v>0.09163103252649307</v>
       </c>
       <c r="C45" s="1">
         <v>36</v>
@@ -2924,7 +2924,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="2">
-        <v>0.09303527325391769</v>
+        <v>0.09163103252649307</v>
       </c>
       <c r="C46" s="1">
         <v>36</v>
@@ -2950,7 +2950,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="2">
-        <v>0.09303527325391769</v>
+        <v>0.09163103252649307</v>
       </c>
       <c r="C47" s="1">
         <v>36</v>
@@ -2976,7 +2976,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="2">
-        <v>0.0826980248093605</v>
+        <v>0.08144980669021606</v>
       </c>
       <c r="C48" s="1">
         <v>32</v>
@@ -3002,7 +3002,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="2">
-        <v>0.07752939313650131</v>
+        <v>0.07635919004678726</v>
       </c>
       <c r="C49" s="1">
         <v>30</v>
@@ -3028,7 +3028,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="2">
-        <v>0.07752939313650131</v>
+        <v>0.07635919004678726</v>
       </c>
       <c r="C50" s="1">
         <v>30</v>
@@ -3054,7 +3054,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="2">
-        <v>0.07752939313650131</v>
+        <v>0.07635919004678726</v>
       </c>
       <c r="C51" s="1">
         <v>30</v>
@@ -3080,7 +3080,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="2">
-        <v>0.07236076891422272</v>
+        <v>0.07126858085393906</v>
       </c>
       <c r="C52" s="1">
         <v>28</v>
@@ -3106,7 +3106,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="2">
-        <v>0.05168626457452774</v>
+        <v>0.05090612918138504</v>
       </c>
       <c r="C53" s="1">
         <v>20</v>
@@ -3132,7 +3132,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="2">
-        <v>0.04651763662695885</v>
+        <v>0.04581551626324654</v>
       </c>
       <c r="C54" s="1">
         <v>18</v>
@@ -3158,7 +3158,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="2">
-        <v>0.03618038445711136</v>
+        <v>0.03563429042696953</v>
       </c>
       <c r="C55" s="1">
         <v>14</v>
@@ -3184,7 +3184,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="2">
-        <v>0.02067450620234013</v>
+        <v>0.02036245167255402</v>
       </c>
       <c r="C56" s="1">
         <v>8</v>
@@ -3210,7 +3210,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="2">
-        <v>0.02067450620234013</v>
+        <v>0.02036245167255402</v>
       </c>
       <c r="C57" s="1">
         <v>8</v>
@@ -3236,7 +3236,7 @@
         <v>13</v>
       </c>
       <c r="B58" s="2">
-        <v>0.01033725310117006</v>
+        <v>0.01018122583627701</v>
       </c>
       <c r="C58" s="1">
         <v>4</v>
@@ -3262,7 +3262,7 @@
         <v>57</v>
       </c>
       <c r="B59" s="2">
-        <v>0.01033725310117006</v>
+        <v>0.01018122583627701</v>
       </c>
       <c r="C59" s="1">
         <v>4</v>

--- a/project/MDK_V5/AT32F403ARGT7_EG800AK_analysis.xlsx
+++ b/project/MDK_V5/AT32F403ARGT7_EG800AK_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="69">
   <si>
     <t>AT32F403ARGT7_EG800AK</t>
   </si>
@@ -71,6 +71,9 @@
     <t>printfa.o</t>
   </si>
   <si>
+    <t>app_eg.o</t>
+  </si>
+  <si>
     <t>lwrb.o</t>
   </si>
   <si>
@@ -131,9 +134,6 @@
     <t>at32f403a_407_tmr.o</t>
   </si>
   <si>
-    <t>app_eg.o</t>
-  </si>
-  <si>
     <t>main.o</t>
   </si>
   <si>
@@ -147,6 +147,9 @@
   </si>
   <si>
     <t>uidiv.o</t>
+  </si>
+  <si>
+    <t>strstr.o</t>
   </si>
   <si>
     <t>memseta.o</t>
@@ -308,9 +311,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$60</c:f>
+              <c:f>ram_percent!$A$3:$A$61</c:f>
               <c:strCache>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
@@ -359,7 +362,7 @@
                 <c:pt idx="15">
                   <c:v>system_at32f403a_407.o</c:v>
                 </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="58">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -367,59 +370,59 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$60</c:f>
+              <c:f>ram_percent!$B$3:$B$61</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
-                  <c:v>38.90614318847656</c:v>
+                  <c:v>38.8825798034668</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>31.36504745483398</c:v>
+                  <c:v>31.34605216979981</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>14.93068695068359</c:v>
+                  <c:v>14.92164421081543</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.529808521270752</c:v>
+                  <c:v>6.525853633880615</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.878494024276733</c:v>
+                  <c:v>3.876145124435425</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.818044066429138</c:v>
+                  <c:v>1.816943049430847</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.136277556419373</c:v>
+                  <c:v>1.135589361190796</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.7499431967735291</c:v>
+                  <c:v>0.8100537657737732</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.333308070898056</c:v>
+                  <c:v>0.3331062197685242</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.2424058765172958</c:v>
+                  <c:v>0.2422590702772141</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.03408832848072052</c:v>
+                  <c:v>0.03406768292188644</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.01515036728233099</c:v>
+                  <c:v>0.01514119189232588</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.01515036728233099</c:v>
+                  <c:v>0.01514119189232588</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.01515036728233099</c:v>
+                  <c:v>0.01514119189232588</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.01515036728233099</c:v>
+                  <c:v>0.01514119189232588</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.01515036728233099</c:v>
-                </c:pt>
-                <c:pt idx="57">
+                  <c:v>0.01514119189232588</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -487,119 +490,119 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$60</c:f>
+              <c:f>flash_percent!$A$3:$A$61</c:f>
               <c:strCache>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>eg_service.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>eg_basic.o</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>tasks.o</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>queue.o</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>mc_w.l</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>printfa.o</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>timers.o</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
+                  <c:v>app_eg.o</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>drv_eg.o</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="9">
                   <c:v>lwrb.o</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="10">
                   <c:v>at32f403a_407_crm.o</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>at32f403a_407_usart.o</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="12">
                   <c:v>include_port.o</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="13">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
                   <c:v>mf_w.l</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="15">
                   <c:v>at32f403a_407_dma.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="16">
                   <c:v>at32f403a_407_wk_config.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="17">
                   <c:v>system_at32f403a_407.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="18">
                   <c:v>at32f403a_407_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="19">
                   <c:v>startup_at32f403a_407.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="20">
                   <c:v>at32f403a_407_misc.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
-                  <c:v>eg_basic.o</c:v>
-                </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>log.o</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="22">
                   <c:v>dadd.o</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="23">
                   <c:v>wk_system.o</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="24">
                   <c:v>freertos_app.o</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="25">
                   <c:v>wk_usart.o</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="26">
                   <c:v>at32f403a_407_int.o</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="27">
                   <c:v>list.o</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="28">
                   <c:v>wk_dma.o</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="29">
                   <c:v>dmul.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="30">
                   <c:v>ddiv.o</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="31">
                   <c:v>system_main.o</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="32">
                   <c:v>depilogue.o</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="33">
                   <c:v>at32f403a_407_exint.o</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="34">
                   <c:v>wk_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="35">
                   <c:v>uldiv.o</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="36">
                   <c:v>at32f403a_407_tmr.o</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>app_eg.o</c:v>
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>main.o</c:v>
@@ -617,51 +620,54 @@
                   <c:v>uidiv.o</c:v>
                 </c:pt>
                 <c:pt idx="42">
+                  <c:v>strstr.o</c:v>
+                </c:pt>
+                <c:pt idx="43">
                   <c:v>memseta.o</c:v>
                 </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="44">
                   <c:v>memcpya.o</c:v>
                 </c:pt>
-                <c:pt idx="44">
+                <c:pt idx="45">
                   <c:v>llsshr.o</c:v>
                 </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="46">
                   <c:v>llushr.o</c:v>
                 </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="47">
                   <c:v>strncmp.o</c:v>
                 </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="48">
                   <c:v>llshl.o</c:v>
                 </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="49">
                   <c:v>handlers.o</c:v>
                 </c:pt>
-                <c:pt idx="49">
+                <c:pt idx="50">
                   <c:v>strcmp.o</c:v>
                 </c:pt>
-                <c:pt idx="50">
+                <c:pt idx="51">
                   <c:v>strchr.o</c:v>
                 </c:pt>
-                <c:pt idx="51">
+                <c:pt idx="52">
                   <c:v>wk_debug.o</c:v>
                 </c:pt>
-                <c:pt idx="52">
+                <c:pt idx="53">
                   <c:v>strlen.o</c:v>
                 </c:pt>
-                <c:pt idx="53">
+                <c:pt idx="54">
                   <c:v>entry9a.o</c:v>
                 </c:pt>
-                <c:pt idx="54">
+                <c:pt idx="55">
                   <c:v>entry2.o</c:v>
                 </c:pt>
-                <c:pt idx="55">
+                <c:pt idx="56">
                   <c:v>stdout.o</c:v>
                 </c:pt>
-                <c:pt idx="56">
+                <c:pt idx="57">
                   <c:v>entry5.o</c:v>
                 </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="58">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -669,182 +675,185 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$60</c:f>
+              <c:f>flash_percent!$B$3:$B$61</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
-                  <c:v>16.22632789611816</c:v>
+                  <c:v>14.3766622543335</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>13.13123607635498</c:v>
+                  <c:v>12.99239826202393</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.387089729309082</c:v>
+                  <c:v>11.78823471069336</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.075952053070068</c:v>
+                  <c:v>7.723398685455322</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.788026809692383</c:v>
+                  <c:v>5.897258758544922</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.339747428894043</c:v>
+                  <c:v>4.762204170227051</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.082671642303467</c:v>
+                  <c:v>3.570605754852295</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.599063396453857</c:v>
+                  <c:v>3.461707592010498</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.593972682952881</c:v>
+                  <c:v>3.359091997146606</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.972918033599854</c:v>
+                  <c:v>2.961194515228272</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.881286859512329</c:v>
+                  <c:v>2.957006216049194</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.855833768844605</c:v>
+                  <c:v>2.446022033691406</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.71329665184021</c:v>
+                  <c:v>2.370630979537964</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.326410055160523</c:v>
+                  <c:v>2.34968900680542</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.684992909431458</c:v>
+                  <c:v>2.23241400718689</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.532274484634399</c:v>
+                  <c:v>1.914095997810364</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.455915331840515</c:v>
+                  <c:v>1.386358380317688</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.079209923744202</c:v>
+                  <c:v>1.260706543922424</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.9417634010314941</c:v>
+                  <c:v>1.197880625724793</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.9315821528434753</c:v>
+                  <c:v>0.8879395127296448</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.8832213282585144</c:v>
+                  <c:v>0.7748528718948364</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.8501323461532593</c:v>
+                  <c:v>0.7266863584518433</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.8450417518615723</c:v>
+                  <c:v>0.699461817741394</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.83231520652771</c:v>
+                  <c:v>0.6952733993530273</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.8297699093818665</c:v>
+                  <c:v>0.6848024129867554</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.783954381942749</c:v>
+                  <c:v>0.682708203792572</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.7534106969833374</c:v>
+                  <c:v>0.6450126767158508</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.6668702960014343</c:v>
+                  <c:v>0.6198822855949402</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.5803298950195313</c:v>
+                  <c:v>0.5486795902252197</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.5650580525398254</c:v>
+                  <c:v>0.4774769246578217</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.5574221014976502</c:v>
+                  <c:v>0.4649117290973663</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.4734269976615906</c:v>
+                  <c:v>0.4586291313171387</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.3410710692405701</c:v>
+                  <c:v>0.3895206451416016</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.3359804451465607</c:v>
+                  <c:v>0.2806223928928375</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.2494400292634964</c:v>
+                  <c:v>0.2764340043067932</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.2392588108778</c:v>
+                  <c:v>0.2052313089370728</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.1527183800935745</c:v>
+                  <c:v>0.1968545168638229</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.1323559284210205</c:v>
+                  <c:v>0.1088982447981834</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.1221747100353241</c:v>
+                  <c:v>0.1005214527249336</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.1221747100353241</c:v>
+                  <c:v>0.1005214527249336</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.1221747100353241</c:v>
+                  <c:v>0.1005214527249336</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.1119934841990471</c:v>
+                  <c:v>0.0921446681022644</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.09163103252649307</c:v>
+                  <c:v>0.07539109140634537</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.09163103252649307</c:v>
+                  <c:v>0.07539109140634537</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.09163103252649307</c:v>
+                  <c:v>0.07539109140634537</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.08144980669021606</c:v>
+                  <c:v>0.07539109140634537</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.07635919004678726</c:v>
+                  <c:v>0.06701430678367615</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.07635919004678726</c:v>
+                  <c:v>0.06282591074705124</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.07635919004678726</c:v>
+                  <c:v>0.06282591074705124</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.07126858085393906</c:v>
+                  <c:v>0.06282591074705124</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.05090612918138504</c:v>
+                  <c:v>0.05863751471042633</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.04581551626324654</c:v>
+                  <c:v>0.04188393801450729</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.03563429042696953</c:v>
+                  <c:v>0.03769554570317268</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.02036245167255402</c:v>
+                  <c:v>0.02931875735521317</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.02036245167255402</c:v>
+                  <c:v>0.01675357669591904</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.01018122583627701</c:v>
+                  <c:v>0.01675357669591904</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.01018122583627701</c:v>
+                  <c:v>0.008376788347959518</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>0.008376788347959518</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -949,8 +958,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H60" totalsRowCount="1">
-  <autoFilter ref="A2:H59"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H61" totalsRowCount="1">
+  <autoFilter ref="A2:H60"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -966,8 +975,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H60" totalsRowCount="1">
-  <autoFilter ref="A2:H59"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H61" totalsRowCount="1">
+  <autoFilter ref="A2:H60"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -1267,7 +1276,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1280,28 +1289,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1309,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>38.90614318847656</v>
+        <v>38.8825798034668</v>
       </c>
       <c r="C3" s="1">
         <v>10272</v>
@@ -1335,7 +1344,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>31.36504745483398</v>
+        <v>31.34605216979981</v>
       </c>
       <c r="C4" s="1">
         <v>8281</v>
@@ -1361,16 +1370,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>14.93068695068359</v>
+        <v>14.92164421081543</v>
       </c>
       <c r="C5" s="1">
         <v>3942</v>
       </c>
       <c r="D5" s="1">
-        <v>6375</v>
+        <v>6865</v>
       </c>
       <c r="E5" s="1">
-        <v>5558</v>
+        <v>6048</v>
       </c>
       <c r="F5" s="1">
         <v>817</v>
@@ -1387,7 +1396,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>6.529808521270752</v>
+        <v>6.525853633880615</v>
       </c>
       <c r="C6" s="1">
         <v>1724</v>
@@ -1413,7 +1422,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>3.878494024276733</v>
+        <v>3.876145124435425</v>
       </c>
       <c r="C7" s="1">
         <v>1024</v>
@@ -1439,16 +1448,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>1.818044066429138</v>
+        <v>1.816943049430847</v>
       </c>
       <c r="C8" s="1">
         <v>480</v>
       </c>
       <c r="D8" s="1">
-        <v>5159</v>
+        <v>5629</v>
       </c>
       <c r="E8" s="1">
-        <v>5150</v>
+        <v>5620</v>
       </c>
       <c r="F8" s="1">
         <v>9</v>
@@ -1465,7 +1474,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>1.136277556419373</v>
+        <v>1.135589361190796</v>
       </c>
       <c r="C9" s="1">
         <v>300</v>
@@ -1491,25 +1500,25 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.7499431967735291</v>
+        <v>0.8100537657737732</v>
       </c>
       <c r="C10" s="1">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="D10" s="1">
-        <v>366</v>
+        <v>6204</v>
       </c>
       <c r="E10" s="1">
-        <v>242</v>
+        <v>5358</v>
       </c>
       <c r="F10" s="1">
-        <v>124</v>
+        <v>846</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>198</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1517,7 +1526,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.333308070898056</v>
+        <v>0.3331062197685242</v>
       </c>
       <c r="C11" s="1">
         <v>88</v>
@@ -1543,7 +1552,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.2424058765172958</v>
+        <v>0.2422590702772141</v>
       </c>
       <c r="C12" s="1">
         <v>64</v>
@@ -1569,7 +1578,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.03408832848072052</v>
+        <v>0.03406768292188644</v>
       </c>
       <c r="C13" s="1">
         <v>9</v>
@@ -1595,16 +1604,16 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.01515036728233099</v>
+        <v>0.01514119189232588</v>
       </c>
       <c r="C14" s="1">
         <v>4</v>
       </c>
       <c r="D14" s="1">
-        <v>2780</v>
+        <v>2816</v>
       </c>
       <c r="E14" s="1">
-        <v>2776</v>
+        <v>2812</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -1621,7 +1630,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.01515036728233099</v>
+        <v>0.01514119189232588</v>
       </c>
       <c r="C15" s="1">
         <v>4</v>
@@ -1647,7 +1656,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.01515036728233099</v>
+        <v>0.01514119189232588</v>
       </c>
       <c r="C16" s="1">
         <v>4</v>
@@ -1673,7 +1682,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.01515036728233099</v>
+        <v>0.01514119189232588</v>
       </c>
       <c r="C17" s="1">
         <v>4</v>
@@ -1699,7 +1708,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.01515036728233099</v>
+        <v>0.01514119189232588</v>
       </c>
       <c r="C18" s="1">
         <v>4</v>
@@ -1720,35 +1729,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
-      <c r="A60" t="s">
-        <v>59</v>
-      </c>
-      <c r="B60">
+    <row r="61" spans="1:8">
+      <c r="A61" t="s">
+        <v>60</v>
+      </c>
+      <c r="B61">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C60">
+      <c r="C61">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D60">
+      <c r="D61">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E60">
+      <c r="E61">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F60">
+      <c r="F61">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G60">
+      <c r="G61">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H60">
+      <c r="H61">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -1764,7 +1773,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1777,28 +1786,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H2" t="s">
         <v>67</v>
-      </c>
-      <c r="C2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H2" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1806,16 +1815,16 @@
         <v>3</v>
       </c>
       <c r="B3" s="2">
-        <v>16.22632789611816</v>
+        <v>14.3766622543335</v>
       </c>
       <c r="C3" s="1">
-        <v>6375</v>
+        <v>6865</v>
       </c>
       <c r="D3" s="1">
         <v>3942</v>
       </c>
       <c r="E3" s="1">
-        <v>5558</v>
+        <v>6048</v>
       </c>
       <c r="F3" s="1">
         <v>817</v>
@@ -1829,103 +1838,103 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" s="2">
-        <v>13.13123607635498</v>
+        <v>12.99239826202393</v>
       </c>
       <c r="C4" s="1">
-        <v>5159</v>
+        <v>6204</v>
       </c>
       <c r="D4" s="1">
-        <v>480</v>
+        <v>214</v>
       </c>
       <c r="E4" s="1">
-        <v>5150</v>
+        <v>5358</v>
       </c>
       <c r="F4" s="1">
-        <v>9</v>
+        <v>846</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>480</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B5" s="2">
-        <v>9.387089729309082</v>
+        <v>11.78823471069336</v>
       </c>
       <c r="C5" s="1">
-        <v>3688</v>
+        <v>5629</v>
       </c>
       <c r="D5" s="1">
-        <v>64</v>
+        <v>480</v>
       </c>
       <c r="E5" s="1">
-        <v>3688</v>
+        <v>5620</v>
       </c>
       <c r="F5" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>64</v>
+        <v>480</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B6" s="2">
-        <v>7.075952053070068</v>
+        <v>7.723398685455322</v>
       </c>
       <c r="C6" s="1">
-        <v>2780</v>
+        <v>3688</v>
       </c>
       <c r="D6" s="1">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="E6" s="1">
-        <v>2776</v>
+        <v>3688</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B7" s="2">
-        <v>5.788026809692383</v>
+        <v>5.897258758544922</v>
       </c>
       <c r="C7" s="1">
-        <v>2274</v>
+        <v>2816</v>
       </c>
       <c r="D7" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E7" s="1">
-        <v>2274</v>
+        <v>2812</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
@@ -1933,54 +1942,54 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B8" s="2">
-        <v>4.339747428894043</v>
+        <v>4.762204170227051</v>
       </c>
       <c r="C8" s="1">
-        <v>1705</v>
+        <v>2274</v>
       </c>
       <c r="D8" s="1">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E8" s="1">
-        <v>1692</v>
+        <v>2274</v>
       </c>
       <c r="F8" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>4.082671642303467</v>
+        <v>3.570605754852295</v>
       </c>
       <c r="C9" s="1">
-        <v>1604</v>
+        <v>1705</v>
       </c>
       <c r="D9" s="1">
-        <v>8281</v>
+        <v>300</v>
       </c>
       <c r="E9" s="1">
-        <v>1442</v>
+        <v>1692</v>
       </c>
       <c r="F9" s="1">
-        <v>162</v>
+        <v>13</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>8281</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1988,19 +1997,19 @@
         <v>18</v>
       </c>
       <c r="B10" s="2">
-        <v>3.599063396453857</v>
+        <v>3.461707592010498</v>
       </c>
       <c r="C10" s="1">
-        <v>1414</v>
+        <v>1653</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
       </c>
       <c r="E10" s="1">
-        <v>1414</v>
+        <v>944</v>
       </c>
       <c r="F10" s="1">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -2011,45 +2020,45 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B11" s="2">
-        <v>3.593972682952881</v>
+        <v>3.359091997146606</v>
       </c>
       <c r="C11" s="1">
-        <v>1412</v>
+        <v>1604</v>
       </c>
       <c r="D11" s="1">
-        <v>0</v>
+        <v>8281</v>
       </c>
       <c r="E11" s="1">
-        <v>1372</v>
+        <v>1442</v>
       </c>
       <c r="F11" s="1">
-        <v>40</v>
+        <v>162</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>0</v>
+        <v>8281</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="2">
-        <v>2.972918033599854</v>
+        <v>2.961194515228272</v>
       </c>
       <c r="C12" s="1">
-        <v>1168</v>
+        <v>1414</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
       </c>
       <c r="E12" s="1">
-        <v>1168</v>
+        <v>1414</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -2063,45 +2072,45 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B13" s="2">
-        <v>2.881286859512329</v>
+        <v>2.957006216049194</v>
       </c>
       <c r="C13" s="1">
-        <v>1132</v>
+        <v>1412</v>
       </c>
       <c r="D13" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E13" s="1">
-        <v>1128</v>
+        <v>1372</v>
       </c>
       <c r="F13" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G13" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="B14" s="2">
-        <v>2.855833768844605</v>
+        <v>2.446022033691406</v>
       </c>
       <c r="C14" s="1">
-        <v>1122</v>
+        <v>1168</v>
       </c>
       <c r="D14" s="1">
-        <v>10272</v>
+        <v>0</v>
       </c>
       <c r="E14" s="1">
-        <v>1122</v>
+        <v>1168</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -2110,50 +2119,50 @@
         <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>10272</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B15" s="2">
-        <v>2.71329665184021</v>
+        <v>2.370630979537964</v>
       </c>
       <c r="C15" s="1">
-        <v>1066</v>
+        <v>1132</v>
       </c>
       <c r="D15" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E15" s="1">
-        <v>1066</v>
+        <v>1128</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="B16" s="2">
-        <v>2.326410055160523</v>
+        <v>2.34968900680542</v>
       </c>
       <c r="C16" s="1">
-        <v>914</v>
+        <v>1122</v>
       </c>
       <c r="D16" s="1">
-        <v>0</v>
+        <v>10272</v>
       </c>
       <c r="E16" s="1">
-        <v>914</v>
+        <v>1122</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -2162,24 +2171,24 @@
         <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>0</v>
+        <v>10272</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B17" s="2">
-        <v>1.684992909431458</v>
+        <v>2.23241400718689</v>
       </c>
       <c r="C17" s="1">
-        <v>662</v>
+        <v>1066</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
       </c>
       <c r="E17" s="1">
-        <v>662</v>
+        <v>1066</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -2193,25 +2202,25 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B18" s="2">
-        <v>1.532274484634399</v>
+        <v>1.914095997810364</v>
       </c>
       <c r="C18" s="1">
-        <v>602</v>
+        <v>914</v>
       </c>
       <c r="D18" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E18" s="1">
-        <v>582</v>
+        <v>914</v>
       </c>
       <c r="F18" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H18" s="1">
         <v>0</v>
@@ -2222,16 +2231,16 @@
         <v>24</v>
       </c>
       <c r="B19" s="2">
-        <v>1.455915331840515</v>
+        <v>1.386358380317688</v>
       </c>
       <c r="C19" s="1">
-        <v>572</v>
+        <v>662</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
       <c r="E19" s="1">
-        <v>572</v>
+        <v>662</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -2245,28 +2254,28 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>1.079209923744202</v>
+        <v>1.260706543922424</v>
       </c>
       <c r="C20" s="1">
-        <v>424</v>
+        <v>602</v>
       </c>
       <c r="D20" s="1">
-        <v>1024</v>
+        <v>4</v>
       </c>
       <c r="E20" s="1">
-        <v>36</v>
+        <v>582</v>
       </c>
       <c r="F20" s="1">
-        <v>388</v>
+        <v>16</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H20" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -2274,16 +2283,16 @@
         <v>25</v>
       </c>
       <c r="B21" s="2">
-        <v>0.9417634010314941</v>
+        <v>1.197880625724793</v>
       </c>
       <c r="C21" s="1">
-        <v>370</v>
+        <v>572</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>370</v>
+        <v>572</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -2297,97 +2306,97 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B22" s="2">
-        <v>0.9315821528434753</v>
+        <v>0.8879395127296448</v>
       </c>
       <c r="C22" s="1">
-        <v>366</v>
+        <v>424</v>
       </c>
       <c r="D22" s="1">
-        <v>198</v>
+        <v>1024</v>
       </c>
       <c r="E22" s="1">
-        <v>242</v>
+        <v>36</v>
       </c>
       <c r="F22" s="1">
-        <v>124</v>
+        <v>388</v>
       </c>
       <c r="G22" s="1">
         <v>0</v>
       </c>
       <c r="H22" s="1">
-        <v>198</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="B23" s="2">
-        <v>0.8832213282585144</v>
+        <v>0.7748528718948364</v>
       </c>
       <c r="C23" s="1">
-        <v>347</v>
+        <v>370</v>
       </c>
       <c r="D23" s="1">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="E23" s="1">
-        <v>336</v>
+        <v>370</v>
       </c>
       <c r="F23" s="1">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G23" s="1">
         <v>0</v>
       </c>
       <c r="H23" s="1">
-        <v>88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B24" s="2">
-        <v>0.8501323461532593</v>
+        <v>0.7266863584518433</v>
       </c>
       <c r="C24" s="1">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="D24" s="1">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="E24" s="1">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F24" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G24" s="1">
         <v>0</v>
       </c>
       <c r="H24" s="1">
-        <v>0</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B25" s="2">
-        <v>0.8450417518615723</v>
+        <v>0.699461817741394</v>
       </c>
       <c r="C25" s="1">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D25" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E25" s="1">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -2396,59 +2405,59 @@
         <v>0</v>
       </c>
       <c r="H25" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="2">
+        <v>0.6952733993530273</v>
+      </c>
+      <c r="C26" s="1">
+        <v>332</v>
+      </c>
+      <c r="D26" s="1">
         <v>4</v>
       </c>
-      <c r="B26" s="2">
-        <v>0.83231520652771</v>
-      </c>
-      <c r="C26" s="1">
-        <v>327</v>
-      </c>
-      <c r="D26" s="1">
-        <v>1724</v>
-      </c>
       <c r="E26" s="1">
-        <v>266</v>
+        <v>332</v>
       </c>
       <c r="F26" s="1">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="G26" s="1">
         <v>0</v>
       </c>
       <c r="H26" s="1">
-        <v>1724</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="B27" s="2">
-        <v>0.8297699093818665</v>
+        <v>0.6848024129867554</v>
       </c>
       <c r="C27" s="1">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D27" s="1">
-        <v>0</v>
+        <v>1724</v>
       </c>
       <c r="E27" s="1">
-        <v>326</v>
+        <v>266</v>
       </c>
       <c r="F27" s="1">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="G27" s="1">
         <v>0</v>
       </c>
       <c r="H27" s="1">
-        <v>0</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -2456,16 +2465,16 @@
         <v>28</v>
       </c>
       <c r="B28" s="2">
-        <v>0.783954381942749</v>
+        <v>0.682708203792572</v>
       </c>
       <c r="C28" s="1">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
       </c>
       <c r="E28" s="1">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -2482,16 +2491,16 @@
         <v>29</v>
       </c>
       <c r="B29" s="2">
-        <v>0.7534106969833374</v>
+        <v>0.6450126767158508</v>
       </c>
       <c r="C29" s="1">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="1">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -2508,16 +2517,16 @@
         <v>30</v>
       </c>
       <c r="B30" s="2">
-        <v>0.6668702960014343</v>
+        <v>0.6198822855949402</v>
       </c>
       <c r="C30" s="1">
-        <v>262</v>
+        <v>296</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
       </c>
       <c r="E30" s="1">
-        <v>262</v>
+        <v>296</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
@@ -2534,16 +2543,16 @@
         <v>31</v>
       </c>
       <c r="B31" s="2">
-        <v>0.5803298950195313</v>
+        <v>0.5486795902252197</v>
       </c>
       <c r="C31" s="1">
-        <v>228</v>
+        <v>262</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
       </c>
       <c r="E31" s="1">
-        <v>228</v>
+        <v>262</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
@@ -2560,16 +2569,16 @@
         <v>32</v>
       </c>
       <c r="B32" s="2">
-        <v>0.5650580525398254</v>
+        <v>0.4774769246578217</v>
       </c>
       <c r="C32" s="1">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
       </c>
       <c r="E32" s="1">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -2583,54 +2592,54 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="B33" s="2">
-        <v>0.5574221014976502</v>
+        <v>0.4649117290973663</v>
       </c>
       <c r="C33" s="1">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D33" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>162</v>
+        <v>222</v>
       </c>
       <c r="F33" s="1">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="G33" s="1">
         <v>0</v>
       </c>
       <c r="H33" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B34" s="2">
-        <v>0.4734269976615906</v>
+        <v>0.4586291313171387</v>
       </c>
       <c r="C34" s="1">
-        <v>186</v>
+        <v>219</v>
       </c>
       <c r="D34" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E34" s="1">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="F34" s="1">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="G34" s="1">
         <v>0</v>
       </c>
       <c r="H34" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -2638,16 +2647,16 @@
         <v>34</v>
       </c>
       <c r="B35" s="2">
-        <v>0.3410710692405701</v>
+        <v>0.3895206451416016</v>
       </c>
       <c r="C35" s="1">
-        <v>134</v>
+        <v>186</v>
       </c>
       <c r="D35" s="1">
         <v>0</v>
       </c>
       <c r="E35" s="1">
-        <v>134</v>
+        <v>186</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -2664,16 +2673,16 @@
         <v>35</v>
       </c>
       <c r="B36" s="2">
-        <v>0.3359804451465607</v>
+        <v>0.2806223928928375</v>
       </c>
       <c r="C36" s="1">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D36" s="1">
         <v>0</v>
       </c>
       <c r="E36" s="1">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
@@ -2690,16 +2699,16 @@
         <v>36</v>
       </c>
       <c r="B37" s="2">
-        <v>0.2494400292634964</v>
+        <v>0.2764340043067932</v>
       </c>
       <c r="C37" s="1">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="D37" s="1">
         <v>0</v>
       </c>
       <c r="E37" s="1">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
@@ -2716,16 +2725,16 @@
         <v>37</v>
       </c>
       <c r="B38" s="2">
-        <v>0.2392588108778</v>
+        <v>0.2052313089370728</v>
       </c>
       <c r="C38" s="1">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D38" s="1">
         <v>0</v>
       </c>
       <c r="E38" s="1">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
@@ -2742,16 +2751,16 @@
         <v>38</v>
       </c>
       <c r="B39" s="2">
-        <v>0.1527183800935745</v>
+        <v>0.1968545168638229</v>
       </c>
       <c r="C39" s="1">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="D39" s="1">
         <v>0</v>
       </c>
       <c r="E39" s="1">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="F39" s="1">
         <v>0</v>
@@ -2768,7 +2777,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="2">
-        <v>0.1323559284210205</v>
+        <v>0.1088982447981834</v>
       </c>
       <c r="C40" s="1">
         <v>52</v>
@@ -2794,7 +2803,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="2">
-        <v>0.1221747100353241</v>
+        <v>0.1005214527249336</v>
       </c>
       <c r="C41" s="1">
         <v>48</v>
@@ -2820,7 +2829,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="2">
-        <v>0.1221747100353241</v>
+        <v>0.1005214527249336</v>
       </c>
       <c r="C42" s="1">
         <v>48</v>
@@ -2846,7 +2855,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="2">
-        <v>0.1221747100353241</v>
+        <v>0.1005214527249336</v>
       </c>
       <c r="C43" s="1">
         <v>48</v>
@@ -2872,7 +2881,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="2">
-        <v>0.1119934841990471</v>
+        <v>0.0921446681022644</v>
       </c>
       <c r="C44" s="1">
         <v>44</v>
@@ -2898,7 +2907,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="2">
-        <v>0.09163103252649307</v>
+        <v>0.07539109140634537</v>
       </c>
       <c r="C45" s="1">
         <v>36</v>
@@ -2924,7 +2933,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="2">
-        <v>0.09163103252649307</v>
+        <v>0.07539109140634537</v>
       </c>
       <c r="C46" s="1">
         <v>36</v>
@@ -2950,7 +2959,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="2">
-        <v>0.09163103252649307</v>
+        <v>0.07539109140634537</v>
       </c>
       <c r="C47" s="1">
         <v>36</v>
@@ -2976,16 +2985,16 @@
         <v>47</v>
       </c>
       <c r="B48" s="2">
-        <v>0.08144980669021606</v>
+        <v>0.07539109140634537</v>
       </c>
       <c r="C48" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D48" s="1">
         <v>0</v>
       </c>
       <c r="E48" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
@@ -3002,16 +3011,16 @@
         <v>48</v>
       </c>
       <c r="B49" s="2">
-        <v>0.07635919004678726</v>
+        <v>0.06701430678367615</v>
       </c>
       <c r="C49" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D49" s="1">
         <v>0</v>
       </c>
       <c r="E49" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
@@ -3028,7 +3037,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="2">
-        <v>0.07635919004678726</v>
+        <v>0.06282591074705124</v>
       </c>
       <c r="C50" s="1">
         <v>30</v>
@@ -3054,7 +3063,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="2">
-        <v>0.07635919004678726</v>
+        <v>0.06282591074705124</v>
       </c>
       <c r="C51" s="1">
         <v>30</v>
@@ -3080,16 +3089,16 @@
         <v>51</v>
       </c>
       <c r="B52" s="2">
-        <v>0.07126858085393906</v>
+        <v>0.06282591074705124</v>
       </c>
       <c r="C52" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
       </c>
       <c r="E52" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
@@ -3106,16 +3115,16 @@
         <v>52</v>
       </c>
       <c r="B53" s="2">
-        <v>0.05090612918138504</v>
+        <v>0.05863751471042633</v>
       </c>
       <c r="C53" s="1">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D53" s="1">
         <v>0</v>
       </c>
       <c r="E53" s="1">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
@@ -3132,16 +3141,16 @@
         <v>53</v>
       </c>
       <c r="B54" s="2">
-        <v>0.04581551626324654</v>
+        <v>0.04188393801450729</v>
       </c>
       <c r="C54" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D54" s="1">
         <v>0</v>
       </c>
       <c r="E54" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F54" s="1">
         <v>0</v>
@@ -3158,16 +3167,16 @@
         <v>54</v>
       </c>
       <c r="B55" s="2">
-        <v>0.03563429042696953</v>
+        <v>0.03769554570317268</v>
       </c>
       <c r="C55" s="1">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D55" s="1">
         <v>0</v>
       </c>
       <c r="E55" s="1">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F55" s="1">
         <v>0</v>
@@ -3184,16 +3193,16 @@
         <v>55</v>
       </c>
       <c r="B56" s="2">
-        <v>0.02036245167255402</v>
+        <v>0.02931875735521317</v>
       </c>
       <c r="C56" s="1">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D56" s="1">
         <v>0</v>
       </c>
       <c r="E56" s="1">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
@@ -3210,7 +3219,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="2">
-        <v>0.02036245167255402</v>
+        <v>0.01675357669591904</v>
       </c>
       <c r="C57" s="1">
         <v>8</v>
@@ -3233,25 +3242,25 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="B58" s="2">
-        <v>0.01018122583627701</v>
+        <v>0.01675357669591904</v>
       </c>
       <c r="C58" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D58" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E58" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F58" s="1">
         <v>0</v>
       </c>
       <c r="G58" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H58" s="1">
         <v>0</v>
@@ -3259,59 +3268,85 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="B59" s="2">
-        <v>0.01018122583627701</v>
+        <v>0.008376788347959518</v>
       </c>
       <c r="C59" s="1">
         <v>4</v>
       </c>
       <c r="D59" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E59" s="1">
+        <v>0</v>
+      </c>
+      <c r="F59" s="1">
+        <v>0</v>
+      </c>
+      <c r="G59" s="1">
         <v>4</v>
       </c>
-      <c r="F59" s="1">
-        <v>0</v>
-      </c>
-      <c r="G59" s="1">
-        <v>0</v>
-      </c>
       <c r="H59" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" t="s">
-        <v>59</v>
-      </c>
-      <c r="B60">
+      <c r="A60" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B60" s="2">
+        <v>0.008376788347959518</v>
+      </c>
+      <c r="C60" s="1">
+        <v>4</v>
+      </c>
+      <c r="D60" s="1">
+        <v>0</v>
+      </c>
+      <c r="E60" s="1">
+        <v>4</v>
+      </c>
+      <c r="F60" s="1">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0</v>
+      </c>
+      <c r="H60" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" t="s">
+        <v>60</v>
+      </c>
+      <c r="B61">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C60">
+      <c r="C61">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D60">
+      <c r="D61">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E60">
+      <c r="E61">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F60">
+      <c r="F61">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G60">
+      <c r="G61">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H60">
+      <c r="H61">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/project/MDK_V5/AT32F403ARGT7_EG800AK_analysis.xlsx
+++ b/project/MDK_V5/AT32F403ARGT7_EG800AK_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="84">
   <si>
     <t>AT32F403ARGT7_EG800AK</t>
   </si>
@@ -47,6 +47,9 @@
     <t>log.o</t>
   </si>
   <si>
+    <t>eg_network.o</t>
+  </si>
+  <si>
     <t>queue.o</t>
   </si>
   <si>
@@ -68,27 +71,33 @@
     <t>system_at32f403a_407.o</t>
   </si>
   <si>
+    <t>app_eg.o</t>
+  </si>
+  <si>
     <t>printfa.o</t>
   </si>
   <si>
-    <t>app_eg.o</t>
-  </si>
-  <si>
     <t>lwrb.o</t>
   </si>
   <si>
     <t>at32f403a_407_crm.o</t>
   </si>
   <si>
+    <t>mf_w.l</t>
+  </si>
+  <si>
     <t>at32f403a_407_usart.o</t>
   </si>
   <si>
-    <t>mf_w.l</t>
-  </si>
-  <si>
     <t>at32f403a_407_dma.o</t>
   </si>
   <si>
+    <t>scanf_fp.o</t>
+  </si>
+  <si>
+    <t>_scanf.o</t>
+  </si>
+  <si>
     <t>at32f403a_407_wk_config.o</t>
   </si>
   <si>
@@ -98,9 +107,15 @@
     <t>at32f403a_407_misc.o</t>
   </si>
   <si>
+    <t>_scanf_longlong.o</t>
+  </si>
+  <si>
     <t>dadd.o</t>
   </si>
   <si>
+    <t>_scanf_int.o</t>
+  </si>
+  <si>
     <t>wk_usart.o</t>
   </si>
   <si>
@@ -116,6 +131,9 @@
     <t>dmul.o</t>
   </si>
   <si>
+    <t>_scanf_str.o</t>
+  </si>
+  <si>
     <t>ddiv.o</t>
   </si>
   <si>
@@ -128,12 +146,27 @@
     <t>wk_gpio.o</t>
   </si>
   <si>
+    <t>fepilogue.o</t>
+  </si>
+  <si>
+    <t>ctype_c.o</t>
+  </si>
+  <si>
     <t>uldiv.o</t>
   </si>
   <si>
     <t>at32f403a_407_tmr.o</t>
   </si>
   <si>
+    <t>_sgetc.o</t>
+  </si>
+  <si>
+    <t>d2f.o</t>
+  </si>
+  <si>
+    <t>sscanf.o</t>
+  </si>
+  <si>
     <t>main.o</t>
   </si>
   <si>
@@ -149,6 +182,9 @@
     <t>uidiv.o</t>
   </si>
   <si>
+    <t>scanf_char.o</t>
+  </si>
+  <si>
     <t>strstr.o</t>
   </si>
   <si>
@@ -176,6 +212,12 @@
     <t>strcmp.o</t>
   </si>
   <si>
+    <t>_chval.o</t>
+  </si>
+  <si>
+    <t>dfltul.o</t>
+  </si>
+  <si>
     <t>strchr.o</t>
   </si>
   <si>
@@ -183,6 +225,9 @@
   </si>
   <si>
     <t>strlen.o</t>
+  </si>
+  <si>
+    <t>isspace_c.o</t>
   </si>
   <si>
     <t>entry9a.o</t>
@@ -311,9 +356,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$61</c:f>
+              <c:f>ram_percent!$A$3:$A$76</c:f>
               <c:strCache>
-                <c:ptCount val="59"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
@@ -342,27 +387,33 @@
                   <c:v>log.o</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>eg_network.o</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>queue.o</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>include_port.o</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>mc_w.l</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>stdout.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>wk_system.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>system_main.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>system_at32f403a_407.o</c:v>
                 </c:pt>
-                <c:pt idx="58">
+                <c:pt idx="17">
+                  <c:v>app_eg.o</c:v>
+                </c:pt>
+                <c:pt idx="73">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -370,59 +421,65 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$61</c:f>
+              <c:f>ram_percent!$B$3:$B$76</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
-                  <c:v>38.8825798034668</c:v>
+                  <c:v>55.834716796875</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>31.34605216979981</c:v>
+                  <c:v>22.54130744934082</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>14.92164421081543</c:v>
+                  <c:v>10.73032665252686</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.525853633880615</c:v>
+                  <c:v>4.692816734313965</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.876145124435425</c:v>
+                  <c:v>2.787380456924439</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.816943049430847</c:v>
+                  <c:v>1.306584596633911</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.135589361190796</c:v>
+                  <c:v>0.8166154026985169</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.8100537657737732</c:v>
+                  <c:v>0.5934072136878967</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.3331062197685242</c:v>
+                  <c:v>0.2395405173301697</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.2422590702772141</c:v>
+                  <c:v>0.1932656466960907</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.03406768292188644</c:v>
+                  <c:v>0.1742112785577774</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.01514119189232588</c:v>
+                  <c:v>0.02449846267700195</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.01514119189232588</c:v>
+                  <c:v>0.01088820490986109</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.01514119189232588</c:v>
+                  <c:v>0.01088820490986109</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.01514119189232588</c:v>
+                  <c:v>0.01088820490986109</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.01514119189232588</c:v>
-                </c:pt>
-                <c:pt idx="58">
+                  <c:v>0.01088820490986109</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.01088820490986109</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.01088820490986109</c:v>
+                </c:pt>
+                <c:pt idx="73">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -490,9 +547,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$61</c:f>
+              <c:f>flash_percent!$A$3:$A$76</c:f>
               <c:strCache>
-                <c:ptCount val="59"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
                   <c:v>eg_service.o</c:v>
                 </c:pt>
@@ -500,174 +557,219 @@
                   <c:v>eg_basic.o</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>eg_network.o</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>tasks.o</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>queue.o</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>mc_w.l</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>app_eg.o</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>queue.o</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>printfa.o</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>timers.o</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>app_eg.o</c:v>
-                </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>drv_eg.o</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>lwrb.o</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>at32f403a_407_crm.o</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
+                  <c:v>mf_w.l</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>at32f403a_407_usart.o</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
                   <c:v>include_port.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="15">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
-                  <c:v>mf_w.l</c:v>
-                </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>at32f403a_407_dma.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
+                  <c:v>scanf_fp.o</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>_scanf.o</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>at32f403a_407_wk_config.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="20">
                   <c:v>system_at32f403a_407.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="21">
                   <c:v>at32f403a_407_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="22">
                   <c:v>startup_at32f403a_407.o</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="23">
                   <c:v>at32f403a_407_misc.o</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="24">
                   <c:v>log.o</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="25">
+                  <c:v>_scanf_longlong.o</c:v>
+                </c:pt>
+                <c:pt idx="26">
                   <c:v>dadd.o</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="27">
+                  <c:v>_scanf_int.o</c:v>
+                </c:pt>
+                <c:pt idx="28">
                   <c:v>wk_system.o</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="29">
                   <c:v>freertos_app.o</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="30">
                   <c:v>wk_usart.o</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="31">
                   <c:v>at32f403a_407_int.o</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="32">
                   <c:v>list.o</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="33">
                   <c:v>wk_dma.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="34">
                   <c:v>dmul.o</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="35">
+                  <c:v>_scanf_str.o</c:v>
+                </c:pt>
+                <c:pt idx="36">
                   <c:v>ddiv.o</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="37">
                   <c:v>system_main.o</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="38">
                   <c:v>depilogue.o</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="39">
                   <c:v>at32f403a_407_exint.o</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="40">
                   <c:v>wk_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="41">
+                  <c:v>fepilogue.o</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>ctype_c.o</c:v>
+                </c:pt>
+                <c:pt idx="43">
                   <c:v>uldiv.o</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="44">
                   <c:v>at32f403a_407_tmr.o</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="45">
+                  <c:v>_sgetc.o</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>d2f.o</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>sscanf.o</c:v>
+                </c:pt>
+                <c:pt idx="48">
                   <c:v>main.o</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="49">
                   <c:v>dfixul.o</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="50">
                   <c:v>cdrcmple.o</c:v>
                 </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="51">
                   <c:v>init.o</c:v>
                 </c:pt>
-                <c:pt idx="41">
+                <c:pt idx="52">
                   <c:v>uidiv.o</c:v>
                 </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="53">
+                  <c:v>scanf_char.o</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>strstr.o</c:v>
                 </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="55">
                   <c:v>memseta.o</c:v>
                 </c:pt>
-                <c:pt idx="44">
+                <c:pt idx="56">
                   <c:v>memcpya.o</c:v>
                 </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="57">
                   <c:v>llsshr.o</c:v>
                 </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="58">
                   <c:v>llushr.o</c:v>
                 </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="59">
                   <c:v>strncmp.o</c:v>
                 </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="60">
                   <c:v>llshl.o</c:v>
                 </c:pt>
-                <c:pt idx="49">
+                <c:pt idx="61">
                   <c:v>handlers.o</c:v>
                 </c:pt>
-                <c:pt idx="50">
+                <c:pt idx="62">
                   <c:v>strcmp.o</c:v>
                 </c:pt>
-                <c:pt idx="51">
+                <c:pt idx="63">
+                  <c:v>_chval.o</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>dfltul.o</c:v>
+                </c:pt>
+                <c:pt idx="65">
                   <c:v>strchr.o</c:v>
                 </c:pt>
-                <c:pt idx="52">
+                <c:pt idx="66">
                   <c:v>wk_debug.o</c:v>
                 </c:pt>
-                <c:pt idx="53">
+                <c:pt idx="67">
                   <c:v>strlen.o</c:v>
                 </c:pt>
-                <c:pt idx="54">
+                <c:pt idx="68">
+                  <c:v>isspace_c.o</c:v>
+                </c:pt>
+                <c:pt idx="69">
                   <c:v>entry9a.o</c:v>
                 </c:pt>
-                <c:pt idx="55">
+                <c:pt idx="70">
                   <c:v>entry2.o</c:v>
                 </c:pt>
-                <c:pt idx="56">
+                <c:pt idx="71">
                   <c:v>stdout.o</c:v>
                 </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="72">
                   <c:v>entry5.o</c:v>
                 </c:pt>
-                <c:pt idx="58">
+                <c:pt idx="73">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -675,185 +777,230 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$61</c:f>
+              <c:f>flash_percent!$B$3:$B$76</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="74"/>
                 <c:pt idx="0">
-                  <c:v>14.3766622543335</c:v>
+                  <c:v>10.83268928527832</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>12.99239826202393</c:v>
+                  <c:v>10.67015933990479</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11.78823471069336</c:v>
+                  <c:v>9.928518295288086</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.723398685455322</c:v>
+                  <c:v>9.480378150939941</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.897258758544922</c:v>
+                  <c:v>9.120603561401367</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.762204170227051</c:v>
+                  <c:v>5.933125972747803</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.570605754852295</c:v>
+                  <c:v>5.819512844085693</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.461707592010498</c:v>
+                  <c:v>3.705047845840454</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.359091997146606</c:v>
+                  <c:v>2.690420150756836</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.961194515228272</c:v>
+                  <c:v>2.50264310836792</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.957006216049194</c:v>
+                  <c:v>2.231234073638916</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.446022033691406</c:v>
+                  <c:v>2.228078126907349</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.370630979537964</c:v>
+                  <c:v>1.981916546821594</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.34968900680542</c:v>
+                  <c:v>1.843056201934815</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.23241400718689</c:v>
+                  <c:v>1.78624963760376</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.914095997810364</c:v>
+                  <c:v>1.770470023155212</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.386358380317688</c:v>
+                  <c:v>1.442254543304443</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.260706543922424</c:v>
+                  <c:v>1.385448098182678</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.197880625724793</c:v>
+                  <c:v>1.281302809715271</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.8879395127296448</c:v>
+                  <c:v>1.044608950614929</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.7748528718948364</c:v>
+                  <c:v>0.9499313831329346</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.7266863584518433</c:v>
+                  <c:v>0.9025925993919373</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.699461817741394</c:v>
+                  <c:v>0.6690546274185181</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.6952733993530273</c:v>
+                  <c:v>0.5838448405265808</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.6848024129867554</c:v>
+                  <c:v>0.5475518107414246</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.682708203792572</c:v>
+                  <c:v>0.5396620035171509</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.6450126767158508</c:v>
+                  <c:v>0.5270383358001709</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.6198822855949402</c:v>
+                  <c:v>0.5238823890686035</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.5486795902252197</c:v>
+                  <c:v>0.5238823890686035</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.4774769246578217</c:v>
+                  <c:v>0.5159926414489746</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.4649117290973663</c:v>
+                  <c:v>0.5144146680831909</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.4586291313171387</c:v>
+                  <c:v>0.4796995520591736</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.3895206451416016</c:v>
+                  <c:v>0.4670758843421936</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.2806223928928375</c:v>
+                  <c:v>0.4134252667427063</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.2764340043067932</c:v>
+                  <c:v>0.3597746789455414</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.2052313089370728</c:v>
+                  <c:v>0.3534628450870514</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.1968545168638229</c:v>
+                  <c:v>0.350306898355484</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.1088982447981834</c:v>
+                  <c:v>0.3455730378627777</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.1005214527249336</c:v>
+                  <c:v>0.2935003936290741</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.1005214527249336</c:v>
+                  <c:v>0.2114465087652206</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.1005214527249336</c:v>
+                  <c:v>0.2082905918359757</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.0921446681022644</c:v>
+                  <c:v>0.1735754907131195</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.07539109140634537</c:v>
+                  <c:v>0.1641077399253845</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.07539109140634537</c:v>
+                  <c:v>0.1546399891376495</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.07539109140634537</c:v>
+                  <c:v>0.1483281552791596</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.07539109140634537</c:v>
+                  <c:v>0.1009893789887428</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.06701430678367615</c:v>
+                  <c:v>0.08836571127176285</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.06282591074705124</c:v>
+                  <c:v>0.08836571127176285</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.06282591074705124</c:v>
+                  <c:v>0.08205386996269226</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.06282591074705124</c:v>
+                  <c:v>0.07574203610420227</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.05863751471042633</c:v>
+                  <c:v>0.07574203610420227</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.04188393801450729</c:v>
+                  <c:v>0.07574203610420227</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.03769554570317268</c:v>
+                  <c:v>0.06943020224571228</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.02931875735521317</c:v>
+                  <c:v>0.06311836093664169</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.01675357669591904</c:v>
+                  <c:v>0.0568065270781517</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.01675357669591904</c:v>
+                  <c:v>0.0568065270781517</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.008376788347959518</c:v>
+                  <c:v>0.0568065270781517</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.008376788347959518</c:v>
+                  <c:v>0.0568065270781517</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>0.05049468949437141</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.04733877256512642</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.04733877256512642</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.04733877256512642</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.04418285563588142</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.04418285563588142</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.03787101805210114</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.03155918046832085</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.02840326353907585</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.02209142781794071</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.01577959023416042</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.01262367237359285</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.01262367237359285</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.006311836186796427</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.006311836186796427</c:v>
+                </c:pt>
+                <c:pt idx="73">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -958,8 +1105,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H61" totalsRowCount="1">
-  <autoFilter ref="A2:H60"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H76" totalsRowCount="1">
+  <autoFilter ref="A2:H75"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -975,8 +1122,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H61" totalsRowCount="1">
-  <autoFilter ref="A2:H60"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H76" totalsRowCount="1">
+  <autoFilter ref="A2:H75"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -1276,7 +1423,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1289,28 +1436,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="E2" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="G2" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="H2" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1318,10 +1465,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>38.8825798034668</v>
+        <v>55.834716796875</v>
       </c>
       <c r="C3" s="1">
-        <v>10272</v>
+        <v>20512</v>
       </c>
       <c r="D3" s="1">
         <v>1122</v>
@@ -1336,7 +1483,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="1">
-        <v>10272</v>
+        <v>20512</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1344,16 +1491,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>31.34605216979981</v>
+        <v>22.54130744934082</v>
       </c>
       <c r="C4" s="1">
         <v>8281</v>
       </c>
       <c r="D4" s="1">
-        <v>1604</v>
+        <v>1586</v>
       </c>
       <c r="E4" s="1">
-        <v>1442</v>
+        <v>1424</v>
       </c>
       <c r="F4" s="1">
         <v>162</v>
@@ -1370,7 +1517,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>14.92164421081543</v>
+        <v>10.73032665252686</v>
       </c>
       <c r="C5" s="1">
         <v>3942</v>
@@ -1396,7 +1543,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>6.525853633880615</v>
+        <v>4.692816734313965</v>
       </c>
       <c r="C6" s="1">
         <v>1724</v>
@@ -1422,7 +1569,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>3.876145124435425</v>
+        <v>2.787380456924439</v>
       </c>
       <c r="C7" s="1">
         <v>1024</v>
@@ -1448,19 +1595,19 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>1.816943049430847</v>
+        <v>1.306584596633911</v>
       </c>
       <c r="C8" s="1">
         <v>480</v>
       </c>
       <c r="D8" s="1">
-        <v>5629</v>
+        <v>6008</v>
       </c>
       <c r="E8" s="1">
-        <v>5620</v>
+        <v>6004</v>
       </c>
       <c r="F8" s="1">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -1474,7 +1621,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>1.135589361190796</v>
+        <v>0.8166154026985169</v>
       </c>
       <c r="C9" s="1">
         <v>300</v>
@@ -1500,25 +1647,25 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.8100537657737732</v>
+        <v>0.5934072136878967</v>
       </c>
       <c r="C10" s="1">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="D10" s="1">
-        <v>6204</v>
+        <v>6762</v>
       </c>
       <c r="E10" s="1">
-        <v>5358</v>
+        <v>5842</v>
       </c>
       <c r="F10" s="1">
-        <v>846</v>
+        <v>920</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1526,7 +1673,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.3331062197685242</v>
+        <v>0.2395405173301697</v>
       </c>
       <c r="C11" s="1">
         <v>88</v>
@@ -1552,25 +1699,25 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.2422590702772141</v>
+        <v>0.1932656466960907</v>
       </c>
       <c r="C12" s="1">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="D12" s="1">
-        <v>3688</v>
+        <v>6292</v>
       </c>
       <c r="E12" s="1">
-        <v>3688</v>
+        <v>4672</v>
       </c>
       <c r="F12" s="1">
-        <v>0</v>
+        <v>1620</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>64</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1578,25 +1725,25 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.03406768292188644</v>
+        <v>0.1742112785577774</v>
       </c>
       <c r="C13" s="1">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="D13" s="1">
-        <v>1132</v>
+        <v>3688</v>
       </c>
       <c r="E13" s="1">
-        <v>1128</v>
+        <v>3688</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1604,16 +1751,16 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.01514119189232588</v>
+        <v>0.02449846267700195</v>
       </c>
       <c r="C14" s="1">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D14" s="1">
-        <v>2816</v>
+        <v>1132</v>
       </c>
       <c r="E14" s="1">
-        <v>2812</v>
+        <v>1128</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -1622,7 +1769,7 @@
         <v>4</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1630,19 +1777,19 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.01514119189232588</v>
+        <v>0.01088820490986109</v>
       </c>
       <c r="C15" s="1">
         <v>4</v>
       </c>
       <c r="D15" s="1">
-        <v>4</v>
+        <v>5780</v>
       </c>
       <c r="E15" s="1">
-        <v>0</v>
+        <v>5712</v>
       </c>
       <c r="F15" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="G15" s="1">
         <v>4</v>
@@ -1656,25 +1803,25 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.01514119189232588</v>
+        <v>0.01088820490986109</v>
       </c>
       <c r="C16" s="1">
         <v>4</v>
       </c>
       <c r="D16" s="1">
-        <v>332</v>
+        <v>4</v>
       </c>
       <c r="E16" s="1">
-        <v>332</v>
+        <v>0</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H16" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1682,19 +1829,19 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.01514119189232588</v>
+        <v>0.01088820490986109</v>
       </c>
       <c r="C17" s="1">
         <v>4</v>
       </c>
       <c r="D17" s="1">
-        <v>219</v>
+        <v>332</v>
       </c>
       <c r="E17" s="1">
-        <v>162</v>
+        <v>332</v>
       </c>
       <c r="F17" s="1">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
@@ -1708,56 +1855,108 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.01514119189232588</v>
+        <v>0.01088820490986109</v>
       </c>
       <c r="C18" s="1">
         <v>4</v>
       </c>
       <c r="D18" s="1">
+        <v>219</v>
+      </c>
+      <c r="E18" s="1">
+        <v>162</v>
+      </c>
+      <c r="F18" s="1">
+        <v>57</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0.01088820490986109</v>
+      </c>
+      <c r="C19" s="1">
+        <v>4</v>
+      </c>
+      <c r="D19" s="1">
         <v>602</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E19" s="1">
         <v>582</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F19" s="1">
         <v>16</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G19" s="1">
         <v>4</v>
       </c>
-      <c r="H18" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8">
-      <c r="A61" t="s">
-        <v>60</v>
-      </c>
-      <c r="B61">
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="2">
+        <v>0.01088820490986109</v>
+      </c>
+      <c r="C20" s="1">
+        <v>4</v>
+      </c>
+      <c r="D20" s="1">
+        <v>3760</v>
+      </c>
+      <c r="E20" s="1">
+        <v>2004</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1756</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" t="s">
+        <v>75</v>
+      </c>
+      <c r="B76">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C61">
+      <c r="C76">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D61">
+      <c r="D76">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E61">
+      <c r="E76">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F61">
+      <c r="F76">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G61">
+      <c r="G76">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H61">
+      <c r="H76">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -1773,7 +1972,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1786,28 +1985,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="E2" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="G2" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="H2" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1815,7 +2014,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2">
-        <v>14.3766622543335</v>
+        <v>10.83268928527832</v>
       </c>
       <c r="C3" s="1">
         <v>6865</v>
@@ -1841,97 +2040,97 @@
         <v>8</v>
       </c>
       <c r="B4" s="2">
-        <v>12.99239826202393</v>
+        <v>10.67015933990479</v>
       </c>
       <c r="C4" s="1">
-        <v>6204</v>
+        <v>6762</v>
       </c>
       <c r="D4" s="1">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="E4" s="1">
-        <v>5358</v>
+        <v>5842</v>
       </c>
       <c r="F4" s="1">
-        <v>846</v>
+        <v>920</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B5" s="2">
-        <v>11.78823471069336</v>
+        <v>9.928518295288086</v>
       </c>
       <c r="C5" s="1">
-        <v>5629</v>
+        <v>6292</v>
       </c>
       <c r="D5" s="1">
-        <v>480</v>
+        <v>71</v>
       </c>
       <c r="E5" s="1">
-        <v>5620</v>
+        <v>4672</v>
       </c>
       <c r="F5" s="1">
-        <v>9</v>
+        <v>1620</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>480</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B6" s="2">
-        <v>7.723398685455322</v>
+        <v>9.480378150939941</v>
       </c>
       <c r="C6" s="1">
-        <v>3688</v>
+        <v>6008</v>
       </c>
       <c r="D6" s="1">
-        <v>64</v>
+        <v>480</v>
       </c>
       <c r="E6" s="1">
-        <v>3688</v>
+        <v>6004</v>
       </c>
       <c r="F6" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>64</v>
+        <v>480</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" s="2">
-        <v>5.897258758544922</v>
+        <v>9.120603561401367</v>
       </c>
       <c r="C7" s="1">
-        <v>2816</v>
+        <v>5780</v>
       </c>
       <c r="D7" s="1">
         <v>4</v>
       </c>
       <c r="E7" s="1">
-        <v>2812</v>
+        <v>5712</v>
       </c>
       <c r="F7" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="G7" s="1">
         <v>4</v>
@@ -1942,74 +2141,74 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8" s="2">
-        <v>4.762204170227051</v>
+        <v>5.933125972747803</v>
       </c>
       <c r="C8" s="1">
-        <v>2274</v>
+        <v>3760</v>
       </c>
       <c r="D8" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E8" s="1">
-        <v>2274</v>
+        <v>2004</v>
       </c>
       <c r="F8" s="1">
-        <v>0</v>
+        <v>1756</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B9" s="2">
-        <v>3.570605754852295</v>
+        <v>5.819512844085693</v>
       </c>
       <c r="C9" s="1">
-        <v>1705</v>
+        <v>3688</v>
       </c>
       <c r="D9" s="1">
-        <v>300</v>
+        <v>64</v>
       </c>
       <c r="E9" s="1">
-        <v>1692</v>
+        <v>3688</v>
       </c>
       <c r="F9" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>300</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" s="2">
-        <v>3.461707592010498</v>
+        <v>3.705047845840454</v>
       </c>
       <c r="C10" s="1">
-        <v>1653</v>
+        <v>2348</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
       </c>
       <c r="E10" s="1">
-        <v>944</v>
+        <v>2348</v>
       </c>
       <c r="F10" s="1">
-        <v>709</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -2020,54 +2219,54 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B11" s="2">
-        <v>3.359091997146606</v>
+        <v>2.690420150756836</v>
       </c>
       <c r="C11" s="1">
-        <v>1604</v>
+        <v>1705</v>
       </c>
       <c r="D11" s="1">
-        <v>8281</v>
+        <v>300</v>
       </c>
       <c r="E11" s="1">
-        <v>1442</v>
+        <v>1692</v>
       </c>
       <c r="F11" s="1">
-        <v>162</v>
+        <v>13</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>8281</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B12" s="2">
-        <v>2.961194515228272</v>
+        <v>2.50264310836792</v>
       </c>
       <c r="C12" s="1">
-        <v>1414</v>
+        <v>1586</v>
       </c>
       <c r="D12" s="1">
-        <v>0</v>
+        <v>8281</v>
       </c>
       <c r="E12" s="1">
-        <v>1414</v>
+        <v>1424</v>
       </c>
       <c r="F12" s="1">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <v>8281</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -2075,19 +2274,19 @@
         <v>20</v>
       </c>
       <c r="B13" s="2">
-        <v>2.957006216049194</v>
+        <v>2.231234073638916</v>
       </c>
       <c r="C13" s="1">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
       </c>
       <c r="E13" s="1">
-        <v>1372</v>
+        <v>1414</v>
       </c>
       <c r="F13" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -2101,19 +2300,19 @@
         <v>21</v>
       </c>
       <c r="B14" s="2">
-        <v>2.446022033691406</v>
+        <v>2.228078126907349</v>
       </c>
       <c r="C14" s="1">
-        <v>1168</v>
+        <v>1412</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
       </c>
       <c r="E14" s="1">
-        <v>1168</v>
+        <v>1372</v>
       </c>
       <c r="F14" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -2124,45 +2323,45 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B15" s="2">
-        <v>2.370630979537964</v>
+        <v>1.981916546821594</v>
       </c>
       <c r="C15" s="1">
-        <v>1132</v>
+        <v>1256</v>
       </c>
       <c r="D15" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E15" s="1">
-        <v>1128</v>
+        <v>1256</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="B16" s="2">
-        <v>2.34968900680542</v>
+        <v>1.843056201934815</v>
       </c>
       <c r="C16" s="1">
-        <v>1122</v>
+        <v>1168</v>
       </c>
       <c r="D16" s="1">
-        <v>10272</v>
+        <v>0</v>
       </c>
       <c r="E16" s="1">
-        <v>1122</v>
+        <v>1168</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -2171,50 +2370,50 @@
         <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>10272</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B17" s="2">
-        <v>2.23241400718689</v>
+        <v>1.78624963760376</v>
       </c>
       <c r="C17" s="1">
-        <v>1066</v>
+        <v>1132</v>
       </c>
       <c r="D17" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E17" s="1">
-        <v>1066</v>
+        <v>1128</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H17" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="B18" s="2">
-        <v>1.914095997810364</v>
+        <v>1.770470023155212</v>
       </c>
       <c r="C18" s="1">
-        <v>914</v>
+        <v>1122</v>
       </c>
       <c r="D18" s="1">
-        <v>0</v>
+        <v>20512</v>
       </c>
       <c r="E18" s="1">
-        <v>914</v>
+        <v>1122</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -2223,7 +2422,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="1">
-        <v>0</v>
+        <v>20512</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -2231,16 +2430,16 @@
         <v>24</v>
       </c>
       <c r="B19" s="2">
-        <v>1.386358380317688</v>
+        <v>1.442254543304443</v>
       </c>
       <c r="C19" s="1">
-        <v>662</v>
+        <v>914</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
       <c r="E19" s="1">
-        <v>662</v>
+        <v>914</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -2254,25 +2453,25 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B20" s="2">
-        <v>1.260706543922424</v>
+        <v>1.385448098182678</v>
       </c>
       <c r="C20" s="1">
-        <v>602</v>
+        <v>878</v>
       </c>
       <c r="D20" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>582</v>
+        <v>878</v>
       </c>
       <c r="F20" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H20" s="1">
         <v>0</v>
@@ -2280,19 +2479,19 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B21" s="2">
-        <v>1.197880625724793</v>
+        <v>1.281302809715271</v>
       </c>
       <c r="C21" s="1">
-        <v>572</v>
+        <v>812</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>572</v>
+        <v>812</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -2306,51 +2505,51 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B22" s="2">
-        <v>0.8879395127296448</v>
+        <v>1.044608950614929</v>
       </c>
       <c r="C22" s="1">
-        <v>424</v>
+        <v>662</v>
       </c>
       <c r="D22" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>36</v>
+        <v>662</v>
       </c>
       <c r="F22" s="1">
-        <v>388</v>
+        <v>0</v>
       </c>
       <c r="G22" s="1">
         <v>0</v>
       </c>
       <c r="H22" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B23" s="2">
-        <v>0.7748528718948364</v>
+        <v>0.9499313831329346</v>
       </c>
       <c r="C23" s="1">
-        <v>370</v>
+        <v>602</v>
       </c>
       <c r="D23" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E23" s="1">
-        <v>370</v>
+        <v>582</v>
       </c>
       <c r="F23" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H23" s="1">
         <v>0</v>
@@ -2358,71 +2557,71 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="B24" s="2">
-        <v>0.7266863584518433</v>
+        <v>0.9025925993919373</v>
       </c>
       <c r="C24" s="1">
-        <v>347</v>
+        <v>572</v>
       </c>
       <c r="D24" s="1">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="E24" s="1">
-        <v>336</v>
+        <v>572</v>
       </c>
       <c r="F24" s="1">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G24" s="1">
         <v>0</v>
       </c>
       <c r="H24" s="1">
-        <v>88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="B25" s="2">
-        <v>0.699461817741394</v>
+        <v>0.6690546274185181</v>
       </c>
       <c r="C25" s="1">
-        <v>334</v>
+        <v>424</v>
       </c>
       <c r="D25" s="1">
-        <v>0</v>
+        <v>1024</v>
       </c>
       <c r="E25" s="1">
-        <v>334</v>
+        <v>36</v>
       </c>
       <c r="F25" s="1">
-        <v>0</v>
+        <v>388</v>
       </c>
       <c r="G25" s="1">
         <v>0</v>
       </c>
       <c r="H25" s="1">
-        <v>0</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B26" s="2">
-        <v>0.6952733993530273</v>
+        <v>0.5838448405265808</v>
       </c>
       <c r="C26" s="1">
-        <v>332</v>
+        <v>370</v>
       </c>
       <c r="D26" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E26" s="1">
-        <v>332</v>
+        <v>370</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -2431,50 +2630,50 @@
         <v>0</v>
       </c>
       <c r="H26" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B27" s="2">
-        <v>0.6848024129867554</v>
+        <v>0.5475518107414246</v>
       </c>
       <c r="C27" s="1">
-        <v>327</v>
+        <v>347</v>
       </c>
       <c r="D27" s="1">
-        <v>1724</v>
+        <v>88</v>
       </c>
       <c r="E27" s="1">
-        <v>266</v>
+        <v>336</v>
       </c>
       <c r="F27" s="1">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="G27" s="1">
         <v>0</v>
       </c>
       <c r="H27" s="1">
-        <v>1724</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B28" s="2">
-        <v>0.682708203792572</v>
+        <v>0.5396620035171509</v>
       </c>
       <c r="C28" s="1">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
       </c>
       <c r="E28" s="1">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -2488,19 +2687,19 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B29" s="2">
-        <v>0.6450126767158508</v>
+        <v>0.5270383358001709</v>
       </c>
       <c r="C29" s="1">
-        <v>308</v>
+        <v>334</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="1">
-        <v>308</v>
+        <v>334</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -2514,19 +2713,19 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B30" s="2">
-        <v>0.6198822855949402</v>
+        <v>0.5238823890686035</v>
       </c>
       <c r="C30" s="1">
-        <v>296</v>
+        <v>332</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
       </c>
       <c r="E30" s="1">
-        <v>296</v>
+        <v>332</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
@@ -2540,19 +2739,19 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="B31" s="2">
-        <v>0.5486795902252197</v>
+        <v>0.5238823890686035</v>
       </c>
       <c r="C31" s="1">
-        <v>262</v>
+        <v>332</v>
       </c>
       <c r="D31" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E31" s="1">
-        <v>262</v>
+        <v>332</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
@@ -2561,33 +2760,33 @@
         <v>0</v>
       </c>
       <c r="H31" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="B32" s="2">
-        <v>0.4774769246578217</v>
+        <v>0.5159926414489746</v>
       </c>
       <c r="C32" s="1">
-        <v>228</v>
+        <v>327</v>
       </c>
       <c r="D32" s="1">
-        <v>0</v>
+        <v>1724</v>
       </c>
       <c r="E32" s="1">
-        <v>228</v>
+        <v>266</v>
       </c>
       <c r="F32" s="1">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="G32" s="1">
         <v>0</v>
       </c>
       <c r="H32" s="1">
-        <v>0</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -2595,16 +2794,16 @@
         <v>33</v>
       </c>
       <c r="B33" s="2">
-        <v>0.4649117290973663</v>
+        <v>0.5144146680831909</v>
       </c>
       <c r="C33" s="1">
-        <v>222</v>
+        <v>326</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>222</v>
+        <v>326</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
@@ -2618,45 +2817,45 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="B34" s="2">
-        <v>0.4586291313171387</v>
+        <v>0.4796995520591736</v>
       </c>
       <c r="C34" s="1">
-        <v>219</v>
+        <v>304</v>
       </c>
       <c r="D34" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E34" s="1">
-        <v>162</v>
+        <v>304</v>
       </c>
       <c r="F34" s="1">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="G34" s="1">
         <v>0</v>
       </c>
       <c r="H34" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B35" s="2">
-        <v>0.3895206451416016</v>
+        <v>0.4670758843421936</v>
       </c>
       <c r="C35" s="1">
-        <v>186</v>
+        <v>296</v>
       </c>
       <c r="D35" s="1">
         <v>0</v>
       </c>
       <c r="E35" s="1">
-        <v>186</v>
+        <v>296</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -2670,19 +2869,19 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B36" s="2">
-        <v>0.2806223928928375</v>
+        <v>0.4134252667427063</v>
       </c>
       <c r="C36" s="1">
-        <v>134</v>
+        <v>262</v>
       </c>
       <c r="D36" s="1">
         <v>0</v>
       </c>
       <c r="E36" s="1">
-        <v>134</v>
+        <v>262</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
@@ -2696,19 +2895,19 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B37" s="2">
-        <v>0.2764340043067932</v>
+        <v>0.3597746789455414</v>
       </c>
       <c r="C37" s="1">
-        <v>132</v>
+        <v>228</v>
       </c>
       <c r="D37" s="1">
         <v>0</v>
       </c>
       <c r="E37" s="1">
-        <v>132</v>
+        <v>228</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
@@ -2722,19 +2921,19 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B38" s="2">
-        <v>0.2052313089370728</v>
+        <v>0.3534628450870514</v>
       </c>
       <c r="C38" s="1">
-        <v>98</v>
+        <v>224</v>
       </c>
       <c r="D38" s="1">
         <v>0</v>
       </c>
       <c r="E38" s="1">
-        <v>98</v>
+        <v>224</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
@@ -2748,19 +2947,19 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B39" s="2">
-        <v>0.1968545168638229</v>
+        <v>0.350306898355484</v>
       </c>
       <c r="C39" s="1">
-        <v>94</v>
+        <v>222</v>
       </c>
       <c r="D39" s="1">
         <v>0</v>
       </c>
       <c r="E39" s="1">
-        <v>94</v>
+        <v>222</v>
       </c>
       <c r="F39" s="1">
         <v>0</v>
@@ -2774,28 +2973,28 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="B40" s="2">
-        <v>0.1088982447981834</v>
+        <v>0.3455730378627777</v>
       </c>
       <c r="C40" s="1">
-        <v>52</v>
+        <v>219</v>
       </c>
       <c r="D40" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E40" s="1">
-        <v>52</v>
+        <v>162</v>
       </c>
       <c r="F40" s="1">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="G40" s="1">
         <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -2803,16 +3002,16 @@
         <v>40</v>
       </c>
       <c r="B41" s="2">
-        <v>0.1005214527249336</v>
+        <v>0.2935003936290741</v>
       </c>
       <c r="C41" s="1">
-        <v>48</v>
+        <v>186</v>
       </c>
       <c r="D41" s="1">
         <v>0</v>
       </c>
       <c r="E41" s="1">
-        <v>48</v>
+        <v>186</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
@@ -2829,16 +3028,16 @@
         <v>41</v>
       </c>
       <c r="B42" s="2">
-        <v>0.1005214527249336</v>
+        <v>0.2114465087652206</v>
       </c>
       <c r="C42" s="1">
-        <v>48</v>
+        <v>134</v>
       </c>
       <c r="D42" s="1">
         <v>0</v>
       </c>
       <c r="E42" s="1">
-        <v>48</v>
+        <v>134</v>
       </c>
       <c r="F42" s="1">
         <v>0</v>
@@ -2855,16 +3054,16 @@
         <v>42</v>
       </c>
       <c r="B43" s="2">
-        <v>0.1005214527249336</v>
+        <v>0.2082905918359757</v>
       </c>
       <c r="C43" s="1">
-        <v>48</v>
+        <v>132</v>
       </c>
       <c r="D43" s="1">
         <v>0</v>
       </c>
       <c r="E43" s="1">
-        <v>48</v>
+        <v>132</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
@@ -2881,16 +3080,16 @@
         <v>43</v>
       </c>
       <c r="B44" s="2">
-        <v>0.0921446681022644</v>
+        <v>0.1735754907131195</v>
       </c>
       <c r="C44" s="1">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="D44" s="1">
         <v>0</v>
       </c>
       <c r="E44" s="1">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
@@ -2907,19 +3106,19 @@
         <v>44</v>
       </c>
       <c r="B45" s="2">
-        <v>0.07539109140634537</v>
+        <v>0.1641077399253845</v>
       </c>
       <c r="C45" s="1">
-        <v>36</v>
+        <v>104</v>
       </c>
       <c r="D45" s="1">
         <v>0</v>
       </c>
       <c r="E45" s="1">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F45" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="G45" s="1">
         <v>0</v>
@@ -2933,16 +3132,16 @@
         <v>45</v>
       </c>
       <c r="B46" s="2">
-        <v>0.07539109140634537</v>
+        <v>0.1546399891376495</v>
       </c>
       <c r="C46" s="1">
-        <v>36</v>
+        <v>98</v>
       </c>
       <c r="D46" s="1">
         <v>0</v>
       </c>
       <c r="E46" s="1">
-        <v>36</v>
+        <v>98</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
@@ -2959,16 +3158,16 @@
         <v>46</v>
       </c>
       <c r="B47" s="2">
-        <v>0.07539109140634537</v>
+        <v>0.1483281552791596</v>
       </c>
       <c r="C47" s="1">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="D47" s="1">
         <v>0</v>
       </c>
       <c r="E47" s="1">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="F47" s="1">
         <v>0</v>
@@ -2985,16 +3184,16 @@
         <v>47</v>
       </c>
       <c r="B48" s="2">
-        <v>0.07539109140634537</v>
+        <v>0.1009893789887428</v>
       </c>
       <c r="C48" s="1">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="D48" s="1">
         <v>0</v>
       </c>
       <c r="E48" s="1">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
@@ -3011,16 +3210,16 @@
         <v>48</v>
       </c>
       <c r="B49" s="2">
-        <v>0.06701430678367615</v>
+        <v>0.08836571127176285</v>
       </c>
       <c r="C49" s="1">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="D49" s="1">
         <v>0</v>
       </c>
       <c r="E49" s="1">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
@@ -3037,16 +3236,16 @@
         <v>49</v>
       </c>
       <c r="B50" s="2">
-        <v>0.06282591074705124</v>
+        <v>0.08836571127176285</v>
       </c>
       <c r="C50" s="1">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="D50" s="1">
         <v>0</v>
       </c>
       <c r="E50" s="1">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
@@ -3063,16 +3262,16 @@
         <v>50</v>
       </c>
       <c r="B51" s="2">
-        <v>0.06282591074705124</v>
+        <v>0.08205386996269226</v>
       </c>
       <c r="C51" s="1">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
       </c>
       <c r="E51" s="1">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
@@ -3089,16 +3288,16 @@
         <v>51</v>
       </c>
       <c r="B52" s="2">
-        <v>0.06282591074705124</v>
+        <v>0.07574203610420227</v>
       </c>
       <c r="C52" s="1">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
       </c>
       <c r="E52" s="1">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
@@ -3115,16 +3314,16 @@
         <v>52</v>
       </c>
       <c r="B53" s="2">
-        <v>0.05863751471042633</v>
+        <v>0.07574203610420227</v>
       </c>
       <c r="C53" s="1">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D53" s="1">
         <v>0</v>
       </c>
       <c r="E53" s="1">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
@@ -3141,16 +3340,16 @@
         <v>53</v>
       </c>
       <c r="B54" s="2">
-        <v>0.04188393801450729</v>
+        <v>0.07574203610420227</v>
       </c>
       <c r="C54" s="1">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="D54" s="1">
         <v>0</v>
       </c>
       <c r="E54" s="1">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F54" s="1">
         <v>0</v>
@@ -3167,16 +3366,16 @@
         <v>54</v>
       </c>
       <c r="B55" s="2">
-        <v>0.03769554570317268</v>
+        <v>0.06943020224571228</v>
       </c>
       <c r="C55" s="1">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="D55" s="1">
         <v>0</v>
       </c>
       <c r="E55" s="1">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="F55" s="1">
         <v>0</v>
@@ -3193,16 +3392,16 @@
         <v>55</v>
       </c>
       <c r="B56" s="2">
-        <v>0.02931875735521317</v>
+        <v>0.06311836093664169</v>
       </c>
       <c r="C56" s="1">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D56" s="1">
         <v>0</v>
       </c>
       <c r="E56" s="1">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
@@ -3219,16 +3418,16 @@
         <v>56</v>
       </c>
       <c r="B57" s="2">
-        <v>0.01675357669591904</v>
+        <v>0.0568065270781517</v>
       </c>
       <c r="C57" s="1">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="D57" s="1">
         <v>0</v>
       </c>
       <c r="E57" s="1">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="F57" s="1">
         <v>0</v>
@@ -3245,16 +3444,16 @@
         <v>57</v>
       </c>
       <c r="B58" s="2">
-        <v>0.01675357669591904</v>
+        <v>0.0568065270781517</v>
       </c>
       <c r="C58" s="1">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="D58" s="1">
         <v>0</v>
       </c>
       <c r="E58" s="1">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="F58" s="1">
         <v>0</v>
@@ -3268,25 +3467,25 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="B59" s="2">
-        <v>0.008376788347959518</v>
+        <v>0.0568065270781517</v>
       </c>
       <c r="C59" s="1">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="D59" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E59" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F59" s="1">
         <v>0</v>
       </c>
       <c r="G59" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H59" s="1">
         <v>0</v>
@@ -3294,59 +3493,449 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B60" s="2">
-        <v>0.008376788347959518</v>
+        <v>0.0568065270781517</v>
       </c>
       <c r="C60" s="1">
+        <v>36</v>
+      </c>
+      <c r="D60" s="1">
+        <v>0</v>
+      </c>
+      <c r="E60" s="1">
+        <v>36</v>
+      </c>
+      <c r="F60" s="1">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0</v>
+      </c>
+      <c r="H60" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2">
+        <v>0.05049468949437141</v>
+      </c>
+      <c r="C61" s="1">
+        <v>32</v>
+      </c>
+      <c r="D61" s="1">
+        <v>0</v>
+      </c>
+      <c r="E61" s="1">
+        <v>32</v>
+      </c>
+      <c r="F61" s="1">
+        <v>0</v>
+      </c>
+      <c r="G61" s="1">
+        <v>0</v>
+      </c>
+      <c r="H61" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2">
+        <v>0.04733877256512642</v>
+      </c>
+      <c r="C62" s="1">
+        <v>30</v>
+      </c>
+      <c r="D62" s="1">
+        <v>0</v>
+      </c>
+      <c r="E62" s="1">
+        <v>30</v>
+      </c>
+      <c r="F62" s="1">
+        <v>0</v>
+      </c>
+      <c r="G62" s="1">
+        <v>0</v>
+      </c>
+      <c r="H62" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2">
+        <v>0.04733877256512642</v>
+      </c>
+      <c r="C63" s="1">
+        <v>30</v>
+      </c>
+      <c r="D63" s="1">
+        <v>0</v>
+      </c>
+      <c r="E63" s="1">
+        <v>30</v>
+      </c>
+      <c r="F63" s="1">
+        <v>0</v>
+      </c>
+      <c r="G63" s="1">
+        <v>0</v>
+      </c>
+      <c r="H63" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2">
+        <v>0.04733877256512642</v>
+      </c>
+      <c r="C64" s="1">
+        <v>30</v>
+      </c>
+      <c r="D64" s="1">
+        <v>0</v>
+      </c>
+      <c r="E64" s="1">
+        <v>30</v>
+      </c>
+      <c r="F64" s="1">
+        <v>0</v>
+      </c>
+      <c r="G64" s="1">
+        <v>0</v>
+      </c>
+      <c r="H64" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2">
+        <v>0.04418285563588142</v>
+      </c>
+      <c r="C65" s="1">
+        <v>28</v>
+      </c>
+      <c r="D65" s="1">
+        <v>0</v>
+      </c>
+      <c r="E65" s="1">
+        <v>28</v>
+      </c>
+      <c r="F65" s="1">
+        <v>0</v>
+      </c>
+      <c r="G65" s="1">
+        <v>0</v>
+      </c>
+      <c r="H65" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2">
+        <v>0.04418285563588142</v>
+      </c>
+      <c r="C66" s="1">
+        <v>28</v>
+      </c>
+      <c r="D66" s="1">
+        <v>0</v>
+      </c>
+      <c r="E66" s="1">
+        <v>28</v>
+      </c>
+      <c r="F66" s="1">
+        <v>0</v>
+      </c>
+      <c r="G66" s="1">
+        <v>0</v>
+      </c>
+      <c r="H66" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2">
+        <v>0.03787101805210114</v>
+      </c>
+      <c r="C67" s="1">
+        <v>24</v>
+      </c>
+      <c r="D67" s="1">
+        <v>0</v>
+      </c>
+      <c r="E67" s="1">
+        <v>24</v>
+      </c>
+      <c r="F67" s="1">
+        <v>0</v>
+      </c>
+      <c r="G67" s="1">
+        <v>0</v>
+      </c>
+      <c r="H67" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2">
+        <v>0.03155918046832085</v>
+      </c>
+      <c r="C68" s="1">
+        <v>20</v>
+      </c>
+      <c r="D68" s="1">
+        <v>0</v>
+      </c>
+      <c r="E68" s="1">
+        <v>20</v>
+      </c>
+      <c r="F68" s="1">
+        <v>0</v>
+      </c>
+      <c r="G68" s="1">
+        <v>0</v>
+      </c>
+      <c r="H68" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2">
+        <v>0.02840326353907585</v>
+      </c>
+      <c r="C69" s="1">
+        <v>18</v>
+      </c>
+      <c r="D69" s="1">
+        <v>0</v>
+      </c>
+      <c r="E69" s="1">
+        <v>18</v>
+      </c>
+      <c r="F69" s="1">
+        <v>0</v>
+      </c>
+      <c r="G69" s="1">
+        <v>0</v>
+      </c>
+      <c r="H69" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2">
+        <v>0.02209142781794071</v>
+      </c>
+      <c r="C70" s="1">
+        <v>14</v>
+      </c>
+      <c r="D70" s="1">
+        <v>0</v>
+      </c>
+      <c r="E70" s="1">
+        <v>14</v>
+      </c>
+      <c r="F70" s="1">
+        <v>0</v>
+      </c>
+      <c r="G70" s="1">
+        <v>0</v>
+      </c>
+      <c r="H70" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2">
+        <v>0.01577959023416042</v>
+      </c>
+      <c r="C71" s="1">
+        <v>10</v>
+      </c>
+      <c r="D71" s="1">
+        <v>0</v>
+      </c>
+      <c r="E71" s="1">
+        <v>10</v>
+      </c>
+      <c r="F71" s="1">
+        <v>0</v>
+      </c>
+      <c r="G71" s="1">
+        <v>0</v>
+      </c>
+      <c r="H71" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2">
+        <v>0.01262367237359285</v>
+      </c>
+      <c r="C72" s="1">
+        <v>8</v>
+      </c>
+      <c r="D72" s="1">
+        <v>0</v>
+      </c>
+      <c r="E72" s="1">
+        <v>8</v>
+      </c>
+      <c r="F72" s="1">
+        <v>0</v>
+      </c>
+      <c r="G72" s="1">
+        <v>0</v>
+      </c>
+      <c r="H72" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2">
+        <v>0.01262367237359285</v>
+      </c>
+      <c r="C73" s="1">
+        <v>8</v>
+      </c>
+      <c r="D73" s="1">
+        <v>0</v>
+      </c>
+      <c r="E73" s="1">
+        <v>8</v>
+      </c>
+      <c r="F73" s="1">
+        <v>0</v>
+      </c>
+      <c r="G73" s="1">
+        <v>0</v>
+      </c>
+      <c r="H73" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B74" s="2">
+        <v>0.006311836186796427</v>
+      </c>
+      <c r="C74" s="1">
         <v>4</v>
       </c>
-      <c r="D60" s="1">
-        <v>0</v>
-      </c>
-      <c r="E60" s="1">
+      <c r="D74" s="1">
         <v>4</v>
       </c>
-      <c r="F60" s="1">
-        <v>0</v>
-      </c>
-      <c r="G60" s="1">
-        <v>0</v>
-      </c>
-      <c r="H60" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8">
-      <c r="A61" t="s">
-        <v>60</v>
-      </c>
-      <c r="B61">
+      <c r="E74" s="1">
+        <v>0</v>
+      </c>
+      <c r="F74" s="1">
+        <v>0</v>
+      </c>
+      <c r="G74" s="1">
+        <v>4</v>
+      </c>
+      <c r="H74" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B75" s="2">
+        <v>0.006311836186796427</v>
+      </c>
+      <c r="C75" s="1">
+        <v>4</v>
+      </c>
+      <c r="D75" s="1">
+        <v>0</v>
+      </c>
+      <c r="E75" s="1">
+        <v>4</v>
+      </c>
+      <c r="F75" s="1">
+        <v>0</v>
+      </c>
+      <c r="G75" s="1">
+        <v>0</v>
+      </c>
+      <c r="H75" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" t="s">
+        <v>75</v>
+      </c>
+      <c r="B76">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C61">
+      <c r="C76">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D61">
+      <c r="D76">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E61">
+      <c r="E76">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F61">
+      <c r="F76">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G61">
+      <c r="G76">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H61">
+      <c r="H76">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
